--- a/excel/templates/XoL_Results.xlsx
+++ b/excel/templates/XoL_Results.xlsx
@@ -13,34 +13,38 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reinsurance Structures" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cedant Impact" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Expiring" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenarios" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="out_params" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="out_loadings" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="out_run_log" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="out_warnings" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="out_recon" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="out_completion_indicated" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="out_bc_summary" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="out_bc_by_year" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="out_annualisation" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="out_large_claims" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="out_fit" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="out_sim_summary" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="out_sim_quantiles" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="out_ev_events" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="out_ev_bc_by_year" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="out_ev_bc_summary" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="out_ev_scenarios" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="out_ev_sim_summary" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="out_ev_sim_quantiles" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="out_attritional_by_year" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="out_gross_summary" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="out_struct_summary" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="out_struct_quantiles" sheetId="30" state="visible" r:id="rId30"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="out_exposed_lives" sheetId="31" state="visible" r:id="rId31"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="out_expiring" sheetId="32" state="visible" r:id="rId32"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="out_asif_by_year" sheetId="33" state="visible" r:id="rId33"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="scn_summary" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Severity" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenarios" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="out_params" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="out_loadings" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="out_run_log" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="out_warnings" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="out_recon" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="out_completion_indicated" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="out_bc_summary" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="out_bc_by_year" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="out_annualisation" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="out_large_claims" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="out_fit" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="out_fit_candidates" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="out_fit_mean_excess" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="out_fit_survival" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="out_sim_summary" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="out_sim_quantiles" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="out_ev_events" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="out_ev_bc_by_year" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="out_ev_bc_summary" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="out_ev_scenarios" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="out_ev_sim_summary" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="out_ev_sim_quantiles" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="out_attritional_by_year" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="out_gross_summary" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="out_struct_summary" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="out_struct_quantiles" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="out_exposed_lives" sheetId="35" state="visible" r:id="rId35"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="out_expiring" sheetId="36" state="visible" r:id="rId36"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="out_asif_by_year" sheetId="37" state="visible" r:id="rId37"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="scn_summary" sheetId="38" state="visible" r:id="rId38"/>
   </sheets>
   <definedNames>
     <definedName name="pa_cedant">INDEX(INDIRECT("'out_params'!$A$2:$BZ$60000"),0,MATCH("cedant",INDIRECT("'out_params'!$A$1:$BZ$1"),0))</definedName>
@@ -78,6 +82,8 @@
     <definedName name="pa_seed">INDEX(INDIRECT("'out_params'!$A$2:$BZ$60000"),0,MATCH("seed",INDIRECT("'out_params'!$A$1:$BZ$1"),0))</definedName>
     <definedName name="pa_fit_cutoff">INDEX(INDIRECT("'out_params'!$A$2:$BZ$60000"),0,MATCH("fit_cutoff",INDIRECT("'out_params'!$A$1:$BZ$1"),0))</definedName>
     <definedName name="pa_fit_candidates">INDEX(INDIRECT("'out_params'!$A$2:$BZ$60000"),0,MATCH("fit_candidates",INDIRECT("'out_params'!$A$1:$BZ$1"),0))</definedName>
+    <definedName name="pa_fit_selected">INDEX(INDIRECT("'out_params'!$A$2:$BZ$60000"),0,MATCH("fit_selected",INDIRECT("'out_params'!$A$1:$BZ$1"),0))</definedName>
+    <definedName name="pa_severity_source">INDEX(INDIRECT("'out_params'!$A$2:$BZ$60000"),0,MATCH("severity_source",INDIRECT("'out_params'!$A$1:$BZ$1"),0))</definedName>
     <definedName name="pa_freq_model">INDEX(INDIRECT("'out_params'!$A$2:$BZ$60000"),0,MATCH("freq_model",INDIRECT("'out_params'!$A$1:$BZ$1"),0))</definedName>
     <definedName name="pa_ev_freq_source">INDEX(INDIRECT("'out_params'!$A$2:$BZ$60000"),0,MATCH("ev_freq_source",INDIRECT("'out_params'!$A$1:$BZ$1"),0))</definedName>
     <definedName name="pa_sl_attritional_threshold">INDEX(INDIRECT("'out_params'!$A$2:$BZ$60000"),0,MATCH("sl_attritional_threshold",INDIRECT("'out_params'!$A$1:$BZ$1"),0))</definedName>
@@ -125,6 +131,39 @@
     <definedName name="bs_expected_cost_det">INDEX(INDIRECT("'out_bc_summary'!$A$2:$BZ$60000"),0,MATCH("expected_cost_det",INDIRECT("'out_bc_summary'!$A$1:$BZ$1"),0))</definedName>
     <definedName name="bs_expected_cost_pct_epi">INDEX(INDIRECT("'out_bc_summary'!$A$2:$BZ$60000"),0,MATCH("expected_cost_pct_epi",INDIRECT("'out_bc_summary'!$A$1:$BZ$1"),0))</definedName>
     <definedName name="bs_expected_cost_from_pct">INDEX(INDIRECT("'out_bc_summary'!$A$2:$BZ$60000"),0,MATCH("expected_cost_from_pct",INDIRECT("'out_bc_summary'!$A$1:$BZ$1"),0))</definedName>
+    <definedName name="fc_dist">INDEX(INDIRECT("'out_fit_candidates'!$A$2:$BZ$60000"),0,MATCH("dist",INDIRECT("'out_fit_candidates'!$A$1:$BZ$1"),0))</definedName>
+    <definedName name="fc_n_params">INDEX(INDIRECT("'out_fit_candidates'!$A$2:$BZ$60000"),0,MATCH("n_params",INDIRECT("'out_fit_candidates'!$A$1:$BZ$1"),0))</definedName>
+    <definedName name="fc_p1_name">INDEX(INDIRECT("'out_fit_candidates'!$A$2:$BZ$60000"),0,MATCH("p1_name",INDIRECT("'out_fit_candidates'!$A$1:$BZ$1"),0))</definedName>
+    <definedName name="fc_p1">INDEX(INDIRECT("'out_fit_candidates'!$A$2:$BZ$60000"),0,MATCH("p1",INDIRECT("'out_fit_candidates'!$A$1:$BZ$1"),0))</definedName>
+    <definedName name="fc_p2_name">INDEX(INDIRECT("'out_fit_candidates'!$A$2:$BZ$60000"),0,MATCH("p2_name",INDIRECT("'out_fit_candidates'!$A$1:$BZ$1"),0))</definedName>
+    <definedName name="fc_p2">INDEX(INDIRECT("'out_fit_candidates'!$A$2:$BZ$60000"),0,MATCH("p2",INDIRECT("'out_fit_candidates'!$A$1:$BZ$1"),0))</definedName>
+    <definedName name="fc_loglik">INDEX(INDIRECT("'out_fit_candidates'!$A$2:$BZ$60000"),0,MATCH("loglik",INDIRECT("'out_fit_candidates'!$A$1:$BZ$1"),0))</definedName>
+    <definedName name="fc_aic">INDEX(INDIRECT("'out_fit_candidates'!$A$2:$BZ$60000"),0,MATCH("aic",INDIRECT("'out_fit_candidates'!$A$1:$BZ$1"),0))</definedName>
+    <definedName name="fc_bic">INDEX(INDIRECT("'out_fit_candidates'!$A$2:$BZ$60000"),0,MATCH("bic",INDIRECT("'out_fit_candidates'!$A$1:$BZ$1"),0))</definedName>
+    <definedName name="fc_ks">INDEX(INDIRECT("'out_fit_candidates'!$A$2:$BZ$60000"),0,MATCH("ks",INDIRECT("'out_fit_candidates'!$A$1:$BZ$1"),0))</definedName>
+    <definedName name="fc_converged">INDEX(INDIRECT("'out_fit_candidates'!$A$2:$BZ$60000"),0,MATCH("converged",INDIRECT("'out_fit_candidates'!$A$1:$BZ$1"),0))</definedName>
+    <definedName name="fc_boundary">INDEX(INDIRECT("'out_fit_candidates'!$A$2:$BZ$60000"),0,MATCH("boundary",INDIRECT("'out_fit_candidates'!$A$1:$BZ$1"),0))</definedName>
+    <definedName name="fc_rank_aic">INDEX(INDIRECT("'out_fit_candidates'!$A$2:$BZ$60000"),0,MATCH("rank_aic",INDIRECT("'out_fit_candidates'!$A$1:$BZ$1"),0))</definedName>
+    <definedName name="fc_rank_bic">INDEX(INDIRECT("'out_fit_candidates'!$A$2:$BZ$60000"),0,MATCH("rank_bic",INDIRECT("'out_fit_candidates'!$A$1:$BZ$1"),0))</definedName>
+    <definedName name="fc_rank_ks">INDEX(INDIRECT("'out_fit_candidates'!$A$2:$BZ$60000"),0,MATCH("rank_ks",INDIRECT("'out_fit_candidates'!$A$1:$BZ$1"),0))</definedName>
+    <definedName name="fc_selected">INDEX(INDIRECT("'out_fit_candidates'!$A$2:$BZ$60000"),0,MATCH("selected",INDIRECT("'out_fit_candidates'!$A$1:$BZ$1"),0))</definedName>
+    <definedName name="fc_me_ratio_min">INDEX(INDIRECT("'out_fit_candidates'!$A$2:$BZ$60000"),0,MATCH("me_ratio_min",INDIRECT("'out_fit_candidates'!$A$1:$BZ$1"),0))</definedName>
+    <definedName name="fc_me_ratio_max">INDEX(INDIRECT("'out_fit_candidates'!$A$2:$BZ$60000"),0,MATCH("me_ratio_max",INDIRECT("'out_fit_candidates'!$A$1:$BZ$1"),0))</definedName>
+    <definedName name="fc_u_fit">INDEX(INDIRECT("'out_fit_candidates'!$A$2:$BZ$60000"),0,MATCH("u_fit",INDIRECT("'out_fit_candidates'!$A$1:$BZ$1"),0))</definedName>
+    <definedName name="fc_max_observed">INDEX(INDIRECT("'out_fit_candidates'!$A$2:$BZ$60000"),0,MATCH("max_observed",INDIRECT("'out_fit_candidates'!$A$1:$BZ$1"),0))</definedName>
+    <definedName name="fc_n_fit">INDEX(INDIRECT("'out_fit_candidates'!$A$2:$BZ$60000"),0,MATCH("n_fit",INDIRECT("'out_fit_candidates'!$A$1:$BZ$1"),0))</definedName>
+    <definedName name="fc_n_uncensored">INDEX(INDIRECT("'out_fit_candidates'!$A$2:$BZ$60000"),0,MATCH("n_uncensored",INDIRECT("'out_fit_candidates'!$A$1:$BZ$1"),0))</definedName>
+    <definedName name="fm_dist">INDEX(INDIRECT("'out_fit_mean_excess'!$A$2:$BZ$60000"),0,MATCH("dist",INDIRECT("'out_fit_mean_excess'!$A$1:$BZ$1"),0))</definedName>
+    <definedName name="fm_ap">INDEX(INDIRECT("'out_fit_mean_excess'!$A$2:$BZ$60000"),0,MATCH("ap",INDIRECT("'out_fit_mean_excess'!$A$1:$BZ$1"),0))</definedName>
+    <definedName name="fm_n_above">INDEX(INDIRECT("'out_fit_mean_excess'!$A$2:$BZ$60000"),0,MATCH("n_above",INDIRECT("'out_fit_mean_excess'!$A$1:$BZ$1"),0))</definedName>
+    <definedName name="fm_mean_excess_empirical">INDEX(INDIRECT("'out_fit_mean_excess'!$A$2:$BZ$60000"),0,MATCH("mean_excess_empirical",INDIRECT("'out_fit_mean_excess'!$A$1:$BZ$1"),0))</definedName>
+    <definedName name="fm_mean_excess_fitted">INDEX(INDIRECT("'out_fit_mean_excess'!$A$2:$BZ$60000"),0,MATCH("mean_excess_fitted",INDIRECT("'out_fit_mean_excess'!$A$1:$BZ$1"),0))</definedName>
+    <definedName name="fm_ratio">INDEX(INDIRECT("'out_fit_mean_excess'!$A$2:$BZ$60000"),0,MATCH("ratio",INDIRECT("'out_fit_mean_excess'!$A$1:$BZ$1"),0))</definedName>
+    <definedName name="fv_dist">INDEX(INDIRECT("'out_fit_survival'!$A$2:$BZ$60000"),0,MATCH("dist",INDIRECT("'out_fit_survival'!$A$1:$BZ$1"),0))</definedName>
+    <definedName name="fv_t">INDEX(INDIRECT("'out_fit_survival'!$A$2:$BZ$60000"),0,MATCH("t",INDIRECT("'out_fit_survival'!$A$1:$BZ$1"),0))</definedName>
+    <definedName name="fv_t_label">INDEX(INDIRECT("'out_fit_survival'!$A$2:$BZ$60000"),0,MATCH("t_label",INDIRECT("'out_fit_survival'!$A$1:$BZ$1"),0))</definedName>
+    <definedName name="fv_s_km">INDEX(INDIRECT("'out_fit_survival'!$A$2:$BZ$60000"),0,MATCH("s_km",INDIRECT("'out_fit_survival'!$A$1:$BZ$1"),0))</definedName>
+    <definedName name="fv_s_fitted">INDEX(INDIRECT("'out_fit_survival'!$A$2:$BZ$60000"),0,MATCH("s_fitted",INDIRECT("'out_fit_survival'!$A$1:$BZ$1"),0))</definedName>
     <definedName name="ps_option_id">INDEX(INDIRECT("'out_sim_summary'!$A$2:$BZ$60000"),0,MATCH("option_id",INDIRECT("'out_sim_summary'!$A$1:$BZ$1"),0))</definedName>
     <definedName name="ps_layer">INDEX(INDIRECT("'out_sim_summary'!$A$2:$BZ$60000"),0,MATCH("layer",INDIRECT("'out_sim_summary'!$A$1:$BZ$1"),0))</definedName>
     <definedName name="ps_l_label">INDEX(INDIRECT("'out_sim_summary'!$A$2:$BZ$60000"),0,MATCH("l_label",INDIRECT("'out_sim_summary'!$A$1:$BZ$1"),0))</definedName>
@@ -134,6 +173,7 @@
     <definedName name="ps_phi">INDEX(INDIRECT("'out_sim_summary'!$A$2:$BZ$60000"),0,MATCH("phi",INDIRECT("'out_sim_summary'!$A$1:$BZ$1"),0))</definedName>
     <definedName name="ps_u_fit">INDEX(INDIRECT("'out_sim_summary'!$A$2:$BZ$60000"),0,MATCH("u_fit",INDIRECT("'out_sim_summary'!$A$1:$BZ$1"),0))</definedName>
     <definedName name="ps_alpha">INDEX(INDIRECT("'out_sim_summary'!$A$2:$BZ$60000"),0,MATCH("alpha",INDIRECT("'out_sim_summary'!$A$1:$BZ$1"),0))</definedName>
+    <definedName name="ps_sev_dist">INDEX(INDIRECT("'out_sim_summary'!$A$2:$BZ$60000"),0,MATCH("sev_dist",INDIRECT("'out_sim_summary'!$A$1:$BZ$1"),0))</definedName>
     <definedName name="ps_max_observed">INDEX(INDIRECT("'out_sim_summary'!$A$2:$BZ$60000"),0,MATCH("max_observed",INDIRECT("'out_sim_summary'!$A$1:$BZ$1"),0))</definedName>
     <definedName name="ps_lives_q">INDEX(INDIRECT("'out_sim_summary'!$A$2:$BZ$60000"),0,MATCH("lives_q",INDIRECT("'out_sim_summary'!$A$1:$BZ$1"),0))</definedName>
     <definedName name="ps_mean_recovery">INDEX(INDIRECT("'out_sim_summary'!$A$2:$BZ$60000"),0,MATCH("mean_recovery",INDIRECT("'out_sim_summary'!$A$1:$BZ$1"),0))</definedName>
@@ -307,7 +347,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="9">
+  <numFmts count="11">
     <numFmt numFmtId="164" formatCode="0.000000"/>
     <numFmt numFmtId="165" formatCode="#,##0;(#,##0);&quot;-&quot;"/>
     <numFmt numFmtId="166" formatCode="0.0%;(0.0%);&quot;-&quot;"/>
@@ -317,6 +357,8 @@
     <numFmt numFmtId="170" formatCode="0.0"/>
     <numFmt numFmtId="171" formatCode="#,##0.0;(#,##0.0);&quot;-&quot;"/>
     <numFmt numFmtId="172" formatCode="#,##0.00##"/>
+    <numFmt numFmtId="173" formatCode="0.0000"/>
+    <numFmt numFmtId="174" formatCode="#,##0.0000"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -404,7 +446,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -461,6 +503,8 @@
     <xf numFmtId="165" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="172" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="173" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="174" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -826,7 +870,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A21"/>
+  <dimension ref="A1:A22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="130" customWidth="1" min="1" max="1"/>
@@ -863,7 +907,7 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2. Run the workflows 00 -&gt; 01 -&gt; 02 -&gt; 03 -&gt; 04 -&gt; 05 -&gt; 06 -&gt; 07 in Alteryx. Stage 07 replaces the data sheets (out_*, scn_summary); close this workbook in Excel before running it.</t>
+          <t>2. Run the workflows 00 -&gt; 01 -&gt; 02 -&gt; 03 -&gt; 04a -&gt; 04 -&gt; 05 -&gt; 06 -&gt; 07 in Alteryx. Stage 07 replaces the data sheets (out_*, scn_summary); close this workbook in Excel before running it.</t>
         </is>
       </c>
     </row>
@@ -922,43 +966,50 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Scenarios - one row per sensitivity run (Params scenario_id).</t>
+          <t>Severity - candidates fitted above u in stage 04a (Python tool): parameters, AIC / BIC / KS, mean excess at each AP and survival against Kaplan-Meier; the distribution the simulation used.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
+          <t>Scenarios - one row per sensitivity run (Params scenario_id).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
           <t>out_* - data written by Alteryx (do not edit; they are replaced each run). out_run_log lists the parameters, justifications, scenario and data mode of the run; out_warnings every check (STOP / FLAG / INFO).</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr"/>
-    </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" s="4" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>Conventions</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>Yellow cells are inputs (blue text). Grey cells show the run value. Formulas read the data sheets through names such as ss_mean_recovery (Formulas &gt; Name Manager), defined with INDIRECT so that a data sheet replaced by Alteryx never breaks a reference.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>No VBA, no Power Query: every calculation is a cell formula.</t>
+          <t>Yellow cells are inputs (blue text). Grey cells show the run value. Formulas read the data sheets through names such as ss_mean_recovery (Formulas &gt; Name Manager), defined with INDIRECT so that a data sheet replaced by Alteryx never breaks a reference.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>No VBA, no Power Query: every calculation is a cell formula.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>Caveats: per-person completion factors from portfolio development may understate development above an attachment point; per-event frequency rests on few events (see credibility); the stop-loss attritional CoV rests on 2-5 annual points (floor applies). Risk transfer and capital are out of scope.</t>
         </is>
@@ -976,23 +1027,38 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>item</t>
+          <t>cover</t>
         </is>
       </c>
       <c r="B1" s="9" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>reinsurer_expense_pct</t>
         </is>
       </c>
       <c r="C1" s="9" t="inlineStr">
         <is>
-          <t>justification</t>
+          <t>brokerage_pct</t>
+        </is>
+      </c>
+      <c r="D1" s="9" t="inlineStr">
+        <is>
+          <t>profit_margin_pct</t>
+        </is>
+      </c>
+      <c r="E1" s="9" t="inlineStr">
+        <is>
+          <t>premium_tax_pct</t>
+        </is>
+      </c>
+      <c r="F1" s="9" t="inlineStr">
+        <is>
+          <t>risk_load_k</t>
         </is>
       </c>
     </row>
@@ -1008,33 +1074,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>stage</t>
+          <t>item</t>
         </is>
       </c>
       <c r="B1" s="9" t="inlineStr">
         <is>
-          <t>code</t>
+          <t>value</t>
         </is>
       </c>
       <c r="C1" s="9" t="inlineStr">
         <is>
-          <t>severity</t>
-        </is>
-      </c>
-      <c r="D1" s="9" t="inlineStr">
-        <is>
-          <t>item</t>
-        </is>
-      </c>
-      <c r="E1" s="9" t="inlineStr">
-        <is>
-          <t>message</t>
+          <t>justification</t>
         </is>
       </c>
     </row>
@@ -1050,7 +1106,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1061,17 +1117,22 @@
       </c>
       <c r="B1" s="9" t="inlineStr">
         <is>
-          <t>table</t>
+          <t>code</t>
         </is>
       </c>
       <c r="C1" s="9" t="inlineStr">
         <is>
-          <t>measure</t>
+          <t>severity</t>
         </is>
       </c>
       <c r="D1" s="9" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="E1" s="9" t="inlineStr">
+        <is>
+          <t>message</t>
         </is>
       </c>
     </row>
@@ -1087,18 +1148,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>ty</t>
+          <t>stage</t>
         </is>
       </c>
       <c r="B1" s="9" t="inlineStr">
         <is>
-          <t>component</t>
+          <t>table</t>
         </is>
       </c>
       <c r="C1" s="9" t="inlineStr">
@@ -1108,12 +1169,7 @@
       </c>
       <c r="D1" s="9" t="inlineStr">
         <is>
-          <t>months_elapsed</t>
-        </is>
-      </c>
-      <c r="E1" s="9" t="inlineStr">
-        <is>
-          <t>indicated_factor</t>
+          <t>value</t>
         </is>
       </c>
     </row>
@@ -1129,153 +1185,33 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC1"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>option_id</t>
+          <t>ty</t>
         </is>
       </c>
       <c r="B1" s="9" t="inlineStr">
         <is>
-          <t>layer</t>
+          <t>component</t>
         </is>
       </c>
       <c r="C1" s="9" t="inlineStr">
         <is>
-          <t>l_label</t>
+          <t>measure</t>
         </is>
       </c>
       <c r="D1" s="9" t="inlineStr">
         <is>
-          <t>lim_basis</t>
+          <t>months_elapsed</t>
         </is>
       </c>
       <c r="E1" s="9" t="inlineStr">
         <is>
-          <t>ap</t>
-        </is>
-      </c>
-      <c r="F1" s="9" t="inlineStr">
-        <is>
-          <t>limit</t>
-        </is>
-      </c>
-      <c r="G1" s="9" t="inlineStr">
-        <is>
-          <t>aad</t>
-        </is>
-      </c>
-      <c r="H1" s="9" t="inlineStr">
-        <is>
-          <t>aal</t>
-        </is>
-      </c>
-      <c r="I1" s="9" t="inlineStr">
-        <is>
-          <t>cop</t>
-        </is>
-      </c>
-      <c r="J1" s="9" t="inlineStr">
-        <is>
-          <t>n_years</t>
-        </is>
-      </c>
-      <c r="K1" s="9" t="inlineStr">
-        <is>
-          <t>n_xl_claims</t>
-        </is>
-      </c>
-      <c r="L1" s="9" t="inlineStr">
-        <is>
-          <t>credibility_z</t>
-        </is>
-      </c>
-      <c r="M1" s="9" t="inlineStr">
-        <is>
-          <t>bc_pppy_weighted_non</t>
-        </is>
-      </c>
-      <c r="N1" s="9" t="inlineStr">
-        <is>
-          <t>bc_pppy_outlier</t>
-        </is>
-      </c>
-      <c r="O1" s="9" t="inlineStr">
-        <is>
-          <t>bc_pppy_total</t>
-        </is>
-      </c>
-      <c r="P1" s="9" t="inlineStr">
-        <is>
-          <t>bc_pct_prem_weighted</t>
-        </is>
-      </c>
-      <c r="Q1" s="9" t="inlineStr">
-        <is>
-          <t>sens_straight_mean</t>
-        </is>
-      </c>
-      <c r="R1" s="9" t="inlineStr">
-        <is>
-          <t>sens_wfreq_x_sev</t>
-        </is>
-      </c>
-      <c r="S1" s="9" t="inlineStr">
-        <is>
-          <t>sens_sfreq_x_sev</t>
-        </is>
-      </c>
-      <c r="T1" s="9" t="inlineStr">
-        <is>
-          <t>bc_min</t>
-        </is>
-      </c>
-      <c r="U1" s="9" t="inlineStr">
-        <is>
-          <t>bc_max</t>
-        </is>
-      </c>
-      <c r="V1" s="9" t="inlineStr">
-        <is>
-          <t>lev_trend</t>
-        </is>
-      </c>
-      <c r="W1" s="9" t="inlineStr">
-        <is>
-          <t>base_trend</t>
-        </is>
-      </c>
-      <c r="X1" s="9" t="inlineStr">
-        <is>
-          <t>leverage_factor</t>
-        </is>
-      </c>
-      <c r="Y1" s="9" t="inlineStr">
-        <is>
-          <t>outlier_thr</t>
-        </is>
-      </c>
-      <c r="Z1" s="9" t="inlineStr">
-        <is>
-          <t>lives_quote_year</t>
-        </is>
-      </c>
-      <c r="AA1" s="9" t="inlineStr">
-        <is>
-          <t>expected_cost_det</t>
-        </is>
-      </c>
-      <c r="AB1" s="9" t="inlineStr">
-        <is>
-          <t>expected_cost_pct_epi</t>
-        </is>
-      </c>
-      <c r="AC1" s="9" t="inlineStr">
-        <is>
-          <t>expected_cost_from_pct</t>
+          <t>indicated_factor</t>
         </is>
       </c>
     </row>
@@ -1291,7 +1227,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W1"/>
+  <dimension ref="A1:AC1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1312,102 +1248,132 @@
       </c>
       <c r="D1" s="9" t="inlineStr">
         <is>
-          <t>ty</t>
+          <t>lim_basis</t>
         </is>
       </c>
       <c r="E1" s="9" t="inlineStr">
         <is>
-          <t>months_elapsed</t>
+          <t>ap</t>
         </is>
       </c>
       <c r="F1" s="9" t="inlineStr">
         <is>
-          <t>exposure_ly_full</t>
+          <t>limit</t>
         </is>
       </c>
       <c r="G1" s="9" t="inlineStr">
         <is>
-          <t>exposure_prem_full</t>
+          <t>aad</t>
         </is>
       </c>
       <c r="H1" s="9" t="inlineStr">
         <is>
-          <t>prem_trend_f</t>
+          <t>aal</t>
         </is>
       </c>
       <c r="I1" s="9" t="inlineStr">
         <is>
-          <t>n_xl</t>
+          <t>cop</t>
         </is>
       </c>
       <c r="J1" s="9" t="inlineStr">
         <is>
-          <t>n_c</t>
+          <t>n_years</t>
         </is>
       </c>
       <c r="K1" s="9" t="inlineStr">
         <is>
-          <t>freq_per_1000</t>
+          <t>n_xl_claims</t>
         </is>
       </c>
       <c r="L1" s="9" t="inlineStr">
         <is>
-          <t>xl</t>
+          <t>credibility_z</t>
         </is>
       </c>
       <c r="M1" s="9" t="inlineStr">
         <is>
-          <t>xl_c</t>
+          <t>bc_pppy_weighted_non</t>
         </is>
       </c>
       <c r="N1" s="9" t="inlineStr">
         <is>
-          <t>severity</t>
+          <t>bc_pppy_outlier</t>
         </is>
       </c>
       <c r="O1" s="9" t="inlineStr">
         <is>
-          <t>xl_aa</t>
+          <t>bc_pppy_total</t>
         </is>
       </c>
       <c r="P1" s="9" t="inlineStr">
         <is>
-          <t>xl_non</t>
+          <t>bc_pct_prem_weighted</t>
         </is>
       </c>
       <c r="Q1" s="9" t="inlineStr">
         <is>
-          <t>xl_out</t>
+          <t>sens_straight_mean</t>
         </is>
       </c>
       <c r="R1" s="9" t="inlineStr">
         <is>
-          <t>bc_pppy</t>
+          <t>sens_wfreq_x_sev</t>
         </is>
       </c>
       <c r="S1" s="9" t="inlineStr">
         <is>
-          <t>bc_pppy_non</t>
+          <t>sens_sfreq_x_sev</t>
         </is>
       </c>
       <c r="T1" s="9" t="inlineStr">
         <is>
-          <t>bc_pppy_out</t>
+          <t>bc_min</t>
         </is>
       </c>
       <c r="U1" s="9" t="inlineStr">
         <is>
-          <t>bc_pct_prem</t>
+          <t>bc_max</t>
         </is>
       </c>
       <c r="V1" s="9" t="inlineStr">
         <is>
-          <t>weight</t>
+          <t>lev_trend</t>
         </is>
       </c>
       <c r="W1" s="9" t="inlineStr">
         <is>
-          <t>weight_out</t>
+          <t>base_trend</t>
+        </is>
+      </c>
+      <c r="X1" s="9" t="inlineStr">
+        <is>
+          <t>leverage_factor</t>
+        </is>
+      </c>
+      <c r="Y1" s="9" t="inlineStr">
+        <is>
+          <t>outlier_thr</t>
+        </is>
+      </c>
+      <c r="Z1" s="9" t="inlineStr">
+        <is>
+          <t>lives_quote_year</t>
+        </is>
+      </c>
+      <c r="AA1" s="9" t="inlineStr">
+        <is>
+          <t>expected_cost_det</t>
+        </is>
+      </c>
+      <c r="AB1" s="9" t="inlineStr">
+        <is>
+          <t>expected_cost_pct_epi</t>
+        </is>
+      </c>
+      <c r="AC1" s="9" t="inlineStr">
+        <is>
+          <t>expected_cost_from_pct</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1389,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:W1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1449,42 +1415,97 @@
       </c>
       <c r="E1" s="9" t="inlineStr">
         <is>
-          <t>xl_reported</t>
+          <t>months_elapsed</t>
         </is>
       </c>
       <c r="F1" s="9" t="inlineStr">
         <is>
-          <t>xl_ibnr</t>
+          <t>exposure_ly_full</t>
         </is>
       </c>
       <c r="G1" s="9" t="inlineStr">
         <is>
-          <t>xl_unearned</t>
+          <t>exposure_prem_full</t>
         </is>
       </c>
       <c r="H1" s="9" t="inlineStr">
         <is>
-          <t>xl_unwritten</t>
+          <t>prem_trend_f</t>
         </is>
       </c>
       <c r="I1" s="9" t="inlineStr">
         <is>
-          <t>n_reported</t>
+          <t>n_xl</t>
         </is>
       </c>
       <c r="J1" s="9" t="inlineStr">
         <is>
-          <t>n_ibnr</t>
+          <t>n_c</t>
         </is>
       </c>
       <c r="K1" s="9" t="inlineStr">
         <is>
-          <t>n_unearned</t>
+          <t>freq_per_1000</t>
         </is>
       </c>
       <c r="L1" s="9" t="inlineStr">
         <is>
-          <t>n_unwritten</t>
+          <t>xl</t>
+        </is>
+      </c>
+      <c r="M1" s="9" t="inlineStr">
+        <is>
+          <t>xl_c</t>
+        </is>
+      </c>
+      <c r="N1" s="9" t="inlineStr">
+        <is>
+          <t>severity</t>
+        </is>
+      </c>
+      <c r="O1" s="9" t="inlineStr">
+        <is>
+          <t>xl_aa</t>
+        </is>
+      </c>
+      <c r="P1" s="9" t="inlineStr">
+        <is>
+          <t>xl_non</t>
+        </is>
+      </c>
+      <c r="Q1" s="9" t="inlineStr">
+        <is>
+          <t>xl_out</t>
+        </is>
+      </c>
+      <c r="R1" s="9" t="inlineStr">
+        <is>
+          <t>bc_pppy</t>
+        </is>
+      </c>
+      <c r="S1" s="9" t="inlineStr">
+        <is>
+          <t>bc_pppy_non</t>
+        </is>
+      </c>
+      <c r="T1" s="9" t="inlineStr">
+        <is>
+          <t>bc_pppy_out</t>
+        </is>
+      </c>
+      <c r="U1" s="9" t="inlineStr">
+        <is>
+          <t>bc_pct_prem</t>
+        </is>
+      </c>
+      <c r="V1" s="9" t="inlineStr">
+        <is>
+          <t>weight</t>
+        </is>
+      </c>
+      <c r="W1" s="9" t="inlineStr">
+        <is>
+          <t>weight_out</t>
         </is>
       </c>
     </row>
@@ -1500,83 +1521,68 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O1"/>
+  <dimension ref="A1:L1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>acc_key</t>
+          <t>option_id</t>
         </is>
       </c>
       <c r="B1" s="9" t="inlineStr">
         <is>
-          <t>member_id</t>
+          <t>layer</t>
         </is>
       </c>
       <c r="C1" s="9" t="inlineStr">
         <is>
+          <t>l_label</t>
+        </is>
+      </c>
+      <c r="D1" s="9" t="inlineStr">
+        <is>
           <t>ty</t>
         </is>
       </c>
-      <c r="D1" s="9" t="inlineStr">
-        <is>
-          <t>segment</t>
-        </is>
-      </c>
       <c r="E1" s="9" t="inlineStr">
         <is>
-          <t>scheme_id</t>
+          <t>xl_reported</t>
         </is>
       </c>
       <c r="F1" s="9" t="inlineStr">
         <is>
-          <t>first_treatment</t>
+          <t>xl_ibnr</t>
         </is>
       </c>
       <c r="G1" s="9" t="inlineStr">
         <is>
-          <t>amount_q</t>
+          <t>xl_unearned</t>
         </is>
       </c>
       <c r="H1" s="9" t="inlineStr">
         <is>
-          <t>trend_f</t>
+          <t>xl_unwritten</t>
         </is>
       </c>
       <c r="I1" s="9" t="inlineStr">
         <is>
-          <t>trended</t>
+          <t>n_reported</t>
         </is>
       </c>
       <c r="J1" s="9" t="inlineStr">
         <is>
-          <t>pre_ap_f</t>
+          <t>n_ibnr</t>
         </is>
       </c>
       <c r="K1" s="9" t="inlineStr">
         <is>
-          <t>adj_uncapped</t>
+          <t>n_unearned</t>
         </is>
       </c>
       <c r="L1" s="9" t="inlineStr">
         <is>
-          <t>cap</t>
-        </is>
-      </c>
-      <c r="M1" s="9" t="inlineStr">
-        <is>
-          <t>adj</t>
-        </is>
-      </c>
-      <c r="N1" s="9" t="inlineStr">
-        <is>
-          <t>outlier</t>
-        </is>
-      </c>
-      <c r="O1" s="9" t="inlineStr">
-        <is>
-          <t>outlier_thr</t>
+          <t>n_unwritten</t>
         </is>
       </c>
     </row>
@@ -1592,73 +1598,83 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:O1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>t</t>
+          <t>acc_key</t>
         </is>
       </c>
       <c r="B1" s="9" t="inlineStr">
         <is>
-          <t>t_label</t>
+          <t>member_id</t>
         </is>
       </c>
       <c r="C1" s="9" t="inlineStr">
         <is>
-          <t>u_fit</t>
+          <t>ty</t>
         </is>
       </c>
       <c r="D1" s="9" t="inlineStr">
         <is>
-          <t>alpha</t>
+          <t>segment</t>
         </is>
       </c>
       <c r="E1" s="9" t="inlineStr">
         <is>
-          <t>alpha_se</t>
+          <t>scheme_id</t>
         </is>
       </c>
       <c r="F1" s="9" t="inlineStr">
         <is>
-          <t>n_fit</t>
+          <t>first_treatment</t>
         </is>
       </c>
       <c r="G1" s="9" t="inlineStr">
         <is>
-          <t>n_uncensored</t>
+          <t>amount_q</t>
         </is>
       </c>
       <c r="H1" s="9" t="inlineStr">
         <is>
-          <t>n_censored</t>
+          <t>trend_f</t>
         </is>
       </c>
       <c r="I1" s="9" t="inlineStr">
         <is>
-          <t>max_observed</t>
+          <t>trended</t>
         </is>
       </c>
       <c r="J1" s="9" t="inlineStr">
         <is>
-          <t>n_ge</t>
+          <t>pre_ap_f</t>
         </is>
       </c>
       <c r="K1" s="9" t="inlineStr">
         <is>
-          <t>expected_n</t>
+          <t>adj_uncapped</t>
         </is>
       </c>
       <c r="L1" s="9" t="inlineStr">
         <is>
-          <t>s_empirical</t>
+          <t>cap</t>
         </is>
       </c>
       <c r="M1" s="9" t="inlineStr">
         <is>
-          <t>s_fitted</t>
+          <t>adj</t>
+        </is>
+      </c>
+      <c r="N1" s="9" t="inlineStr">
+        <is>
+          <t>outlier</t>
+        </is>
+      </c>
+      <c r="O1" s="9" t="inlineStr">
+        <is>
+          <t>outlier_thr</t>
         </is>
       </c>
     </row>
@@ -1674,158 +1690,73 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD1"/>
+  <dimension ref="A1:M1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>option_id</t>
+          <t>t</t>
         </is>
       </c>
       <c r="B1" s="9" t="inlineStr">
         <is>
-          <t>layer</t>
+          <t>t_label</t>
         </is>
       </c>
       <c r="C1" s="9" t="inlineStr">
         <is>
-          <t>l_label</t>
+          <t>u_fit</t>
         </is>
       </c>
       <c r="D1" s="9" t="inlineStr">
         <is>
-          <t>iterations</t>
+          <t>alpha</t>
         </is>
       </c>
       <c r="E1" s="9" t="inlineStr">
         <is>
-          <t>lambda</t>
+          <t>alpha_se</t>
         </is>
       </c>
       <c r="F1" s="9" t="inlineStr">
         <is>
-          <t>freq_dist</t>
+          <t>n_fit</t>
         </is>
       </c>
       <c r="G1" s="9" t="inlineStr">
         <is>
-          <t>phi</t>
+          <t>n_uncensored</t>
         </is>
       </c>
       <c r="H1" s="9" t="inlineStr">
         <is>
-          <t>u_fit</t>
+          <t>n_censored</t>
         </is>
       </c>
       <c r="I1" s="9" t="inlineStr">
         <is>
-          <t>alpha</t>
+          <t>max_observed</t>
         </is>
       </c>
       <c r="J1" s="9" t="inlineStr">
         <is>
-          <t>max_observed</t>
+          <t>n_ge</t>
         </is>
       </c>
       <c r="K1" s="9" t="inlineStr">
         <is>
-          <t>lives_q</t>
+          <t>expected_n</t>
         </is>
       </c>
       <c r="L1" s="9" t="inlineStr">
         <is>
-          <t>mean_recovery</t>
+          <t>s_empirical</t>
         </is>
       </c>
       <c r="M1" s="9" t="inlineStr">
         <is>
-          <t>sd_recovery</t>
-        </is>
-      </c>
-      <c r="N1" s="9" t="inlineStr">
-        <is>
-          <t>cov</t>
-        </is>
-      </c>
-      <c r="O1" s="9" t="inlineStr">
-        <is>
-          <t>p_zero</t>
-        </is>
-      </c>
-      <c r="P1" s="9" t="inlineStr">
-        <is>
-          <t>p50</t>
-        </is>
-      </c>
-      <c r="Q1" s="9" t="inlineStr">
-        <is>
-          <t>p75</t>
-        </is>
-      </c>
-      <c r="R1" s="9" t="inlineStr">
-        <is>
-          <t>p90</t>
-        </is>
-      </c>
-      <c r="S1" s="9" t="inlineStr">
-        <is>
-          <t>p95</t>
-        </is>
-      </c>
-      <c r="T1" s="9" t="inlineStr">
-        <is>
-          <t>p99</t>
-        </is>
-      </c>
-      <c r="U1" s="9" t="inlineStr">
-        <is>
-          <t>p995</t>
-        </is>
-      </c>
-      <c r="V1" s="9" t="inlineStr">
-        <is>
-          <t>max_recovery</t>
-        </is>
-      </c>
-      <c r="W1" s="9" t="inlineStr">
-        <is>
-          <t>mean_below_max_observed</t>
-        </is>
-      </c>
-      <c r="X1" s="9" t="inlineStr">
-        <is>
-          <t>mean_above_max_observed</t>
-        </is>
-      </c>
-      <c r="Y1" s="9" t="inlineStr">
-        <is>
-          <t>mean_reinst_usage</t>
-        </is>
-      </c>
-      <c r="Z1" s="9" t="inlineStr">
-        <is>
-          <t>expected_cost_det</t>
-        </is>
-      </c>
-      <c r="AA1" s="9" t="inlineStr">
-        <is>
-          <t>credibility_z</t>
-        </is>
-      </c>
-      <c r="AB1" s="9" t="inlineStr">
-        <is>
-          <t>det_to_stoch_below</t>
-        </is>
-      </c>
-      <c r="AC1" s="9" t="inlineStr">
-        <is>
-          <t>expected_loss_blended</t>
-        </is>
-      </c>
-      <c r="AD1" s="9" t="inlineStr">
-        <is>
-          <t>expected_loss_pppy</t>
+          <t>s_fitted</t>
         </is>
       </c>
     </row>
@@ -2548,33 +2479,118 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:V1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>option_id</t>
+          <t>dist</t>
         </is>
       </c>
       <c r="B1" s="9" t="inlineStr">
         <is>
-          <t>layer</t>
+          <t>n_params</t>
         </is>
       </c>
       <c r="C1" s="9" t="inlineStr">
         <is>
-          <t>l_label</t>
+          <t>p1_name</t>
         </is>
       </c>
       <c r="D1" s="9" t="inlineStr">
         <is>
-          <t>q</t>
+          <t>p1</t>
         </is>
       </c>
       <c r="E1" s="9" t="inlineStr">
         <is>
-          <t>recovery</t>
+          <t>p2_name</t>
+        </is>
+      </c>
+      <c r="F1" s="9" t="inlineStr">
+        <is>
+          <t>p2</t>
+        </is>
+      </c>
+      <c r="G1" s="9" t="inlineStr">
+        <is>
+          <t>loglik</t>
+        </is>
+      </c>
+      <c r="H1" s="9" t="inlineStr">
+        <is>
+          <t>aic</t>
+        </is>
+      </c>
+      <c r="I1" s="9" t="inlineStr">
+        <is>
+          <t>bic</t>
+        </is>
+      </c>
+      <c r="J1" s="9" t="inlineStr">
+        <is>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="K1" s="9" t="inlineStr">
+        <is>
+          <t>converged</t>
+        </is>
+      </c>
+      <c r="L1" s="9" t="inlineStr">
+        <is>
+          <t>boundary</t>
+        </is>
+      </c>
+      <c r="M1" s="9" t="inlineStr">
+        <is>
+          <t>rank_aic</t>
+        </is>
+      </c>
+      <c r="N1" s="9" t="inlineStr">
+        <is>
+          <t>rank_bic</t>
+        </is>
+      </c>
+      <c r="O1" s="9" t="inlineStr">
+        <is>
+          <t>rank_ks</t>
+        </is>
+      </c>
+      <c r="P1" s="9" t="inlineStr">
+        <is>
+          <t>selected</t>
+        </is>
+      </c>
+      <c r="Q1" s="9" t="inlineStr">
+        <is>
+          <t>me_ratio_min</t>
+        </is>
+      </c>
+      <c r="R1" s="9" t="inlineStr">
+        <is>
+          <t>me_ratio_max</t>
+        </is>
+      </c>
+      <c r="S1" s="9" t="inlineStr">
+        <is>
+          <t>u_fit</t>
+        </is>
+      </c>
+      <c r="T1" s="9" t="inlineStr">
+        <is>
+          <t>max_observed</t>
+        </is>
+      </c>
+      <c r="U1" s="9" t="inlineStr">
+        <is>
+          <t>n_fit</t>
+        </is>
+      </c>
+      <c r="V1" s="9" t="inlineStr">
+        <is>
+          <t>n_uncensored</t>
         </is>
       </c>
     </row>
@@ -2590,68 +2606,38 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>event_key</t>
+          <t>dist</t>
         </is>
       </c>
       <c r="B1" s="9" t="inlineStr">
         <is>
-          <t>ev_src</t>
+          <t>ap</t>
         </is>
       </c>
       <c r="C1" s="9" t="inlineStr">
         <is>
-          <t>ty</t>
+          <t>n_above</t>
         </is>
       </c>
       <c r="D1" s="9" t="inlineStr">
         <is>
-          <t>event_date</t>
+          <t>mean_excess_empirical</t>
         </is>
       </c>
       <c r="E1" s="9" t="inlineStr">
         <is>
-          <t>n_lives</t>
+          <t>mean_excess_fitted</t>
         </is>
       </c>
       <c r="F1" s="9" t="inlineStr">
         <is>
-          <t>scheme_id</t>
-        </is>
-      </c>
-      <c r="G1" s="9" t="inlineStr">
-        <is>
-          <t>site</t>
-        </is>
-      </c>
-      <c r="H1" s="9" t="inlineStr">
-        <is>
-          <t>cause_code</t>
-        </is>
-      </c>
-      <c r="I1" s="9" t="inlineStr">
-        <is>
-          <t>loss_raw</t>
-        </is>
-      </c>
-      <c r="J1" s="9" t="inlineStr">
-        <is>
-          <t>trend_f</t>
-        </is>
-      </c>
-      <c r="K1" s="9" t="inlineStr">
-        <is>
-          <t>loss_adj</t>
-        </is>
-      </c>
-      <c r="L1" s="9" t="inlineStr">
-        <is>
-          <t>loss_net_pp</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -2667,78 +2653,33 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>option_id</t>
+          <t>dist</t>
         </is>
       </c>
       <c r="B1" s="9" t="inlineStr">
         <is>
-          <t>layer</t>
+          <t>t</t>
         </is>
       </c>
       <c r="C1" s="9" t="inlineStr">
         <is>
-          <t>l_label</t>
+          <t>t_label</t>
         </is>
       </c>
       <c r="D1" s="9" t="inlineStr">
         <is>
-          <t>ty</t>
+          <t>s_km</t>
         </is>
       </c>
       <c r="E1" s="9" t="inlineStr">
         <is>
-          <t>exposure_ly_full</t>
-        </is>
-      </c>
-      <c r="F1" s="9" t="inlineStr">
-        <is>
-          <t>n_events</t>
-        </is>
-      </c>
-      <c r="G1" s="9" t="inlineStr">
-        <is>
-          <t>events_per_1000</t>
-        </is>
-      </c>
-      <c r="H1" s="9" t="inlineStr">
-        <is>
-          <t>n_xl</t>
-        </is>
-      </c>
-      <c r="I1" s="9" t="inlineStr">
-        <is>
-          <t>xl</t>
-        </is>
-      </c>
-      <c r="J1" s="9" t="inlineStr">
-        <is>
-          <t>recovery</t>
-        </is>
-      </c>
-      <c r="K1" s="9" t="inlineStr">
-        <is>
-          <t>xl_net</t>
-        </is>
-      </c>
-      <c r="L1" s="9" t="inlineStr">
-        <is>
-          <t>recovery_net</t>
-        </is>
-      </c>
-      <c r="M1" s="9" t="inlineStr">
-        <is>
-          <t>bc_pppy</t>
-        </is>
-      </c>
-      <c r="N1" s="9" t="inlineStr">
-        <is>
-          <t>weight</t>
+          <t>s_fitted</t>
         </is>
       </c>
     </row>
@@ -2754,7 +2695,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:AE1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2775,37 +2716,142 @@
       </c>
       <c r="D1" s="9" t="inlineStr">
         <is>
-          <t>n_events</t>
+          <t>iterations</t>
         </is>
       </c>
       <c r="E1" s="9" t="inlineStr">
         <is>
-          <t>n_xl_events</t>
+          <t>lambda</t>
         </is>
       </c>
       <c r="F1" s="9" t="inlineStr">
         <is>
-          <t>bc_pppy_weighted</t>
+          <t>freq_dist</t>
         </is>
       </c>
       <c r="G1" s="9" t="inlineStr">
         <is>
-          <t>lives_quote_year</t>
+          <t>phi</t>
         </is>
       </c>
       <c r="H1" s="9" t="inlineStr">
         <is>
+          <t>u_fit</t>
+        </is>
+      </c>
+      <c r="I1" s="9" t="inlineStr">
+        <is>
+          <t>alpha</t>
+        </is>
+      </c>
+      <c r="J1" s="9" t="inlineStr">
+        <is>
+          <t>sev_dist</t>
+        </is>
+      </c>
+      <c r="K1" s="9" t="inlineStr">
+        <is>
+          <t>max_observed</t>
+        </is>
+      </c>
+      <c r="L1" s="9" t="inlineStr">
+        <is>
+          <t>lives_q</t>
+        </is>
+      </c>
+      <c r="M1" s="9" t="inlineStr">
+        <is>
+          <t>mean_recovery</t>
+        </is>
+      </c>
+      <c r="N1" s="9" t="inlineStr">
+        <is>
+          <t>sd_recovery</t>
+        </is>
+      </c>
+      <c r="O1" s="9" t="inlineStr">
+        <is>
+          <t>cov</t>
+        </is>
+      </c>
+      <c r="P1" s="9" t="inlineStr">
+        <is>
+          <t>p_zero</t>
+        </is>
+      </c>
+      <c r="Q1" s="9" t="inlineStr">
+        <is>
+          <t>p50</t>
+        </is>
+      </c>
+      <c r="R1" s="9" t="inlineStr">
+        <is>
+          <t>p75</t>
+        </is>
+      </c>
+      <c r="S1" s="9" t="inlineStr">
+        <is>
+          <t>p90</t>
+        </is>
+      </c>
+      <c r="T1" s="9" t="inlineStr">
+        <is>
+          <t>p95</t>
+        </is>
+      </c>
+      <c r="U1" s="9" t="inlineStr">
+        <is>
+          <t>p99</t>
+        </is>
+      </c>
+      <c r="V1" s="9" t="inlineStr">
+        <is>
+          <t>p995</t>
+        </is>
+      </c>
+      <c r="W1" s="9" t="inlineStr">
+        <is>
+          <t>max_recovery</t>
+        </is>
+      </c>
+      <c r="X1" s="9" t="inlineStr">
+        <is>
+          <t>mean_below_max_observed</t>
+        </is>
+      </c>
+      <c r="Y1" s="9" t="inlineStr">
+        <is>
+          <t>mean_above_max_observed</t>
+        </is>
+      </c>
+      <c r="Z1" s="9" t="inlineStr">
+        <is>
+          <t>mean_reinst_usage</t>
+        </is>
+      </c>
+      <c r="AA1" s="9" t="inlineStr">
+        <is>
           <t>expected_cost_det</t>
         </is>
       </c>
-      <c r="I1" s="9" t="inlineStr">
+      <c r="AB1" s="9" t="inlineStr">
         <is>
           <t>credibility_z</t>
         </is>
       </c>
-      <c r="J1" s="9" t="inlineStr">
-        <is>
-          <t>lambda_exp</t>
+      <c r="AC1" s="9" t="inlineStr">
+        <is>
+          <t>det_to_stoch_below</t>
+        </is>
+      </c>
+      <c r="AD1" s="9" t="inlineStr">
+        <is>
+          <t>expected_loss_blended</t>
+        </is>
+      </c>
+      <c r="AE1" s="9" t="inlineStr">
+        <is>
+          <t>expected_loss_pppy</t>
         </is>
       </c>
     </row>
@@ -2821,63 +2867,33 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>scenario_name</t>
+          <t>option_id</t>
         </is>
       </c>
       <c r="B1" s="9" t="inlineStr">
         <is>
-          <t>lives</t>
+          <t>layer</t>
         </is>
       </c>
       <c r="C1" s="9" t="inlineStr">
         <is>
-          <t>cost_per_life</t>
+          <t>l_label</t>
         </is>
       </c>
       <c r="D1" s="9" t="inlineStr">
         <is>
-          <t>return_period_yrs</t>
+          <t>q</t>
         </is>
       </c>
       <c r="E1" s="9" t="inlineStr">
         <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="F1" s="9" t="inlineStr">
-        <is>
-          <t>loss_net_pp</t>
-        </is>
-      </c>
-      <c r="G1" s="9" t="inlineStr">
-        <is>
-          <t>option_id</t>
-        </is>
-      </c>
-      <c r="H1" s="9" t="inlineStr">
-        <is>
-          <t>layer</t>
-        </is>
-      </c>
-      <c r="I1" s="9" t="inlineStr">
-        <is>
-          <t>l_label</t>
-        </is>
-      </c>
-      <c r="J1" s="9" t="inlineStr">
-        <is>
-          <t>layer_loss</t>
-        </is>
-      </c>
-      <c r="K1" s="9" t="inlineStr">
-        <is>
-          <t>layer_loss_net_pp</t>
+          <t>recovery</t>
         </is>
       </c>
     </row>
@@ -2893,123 +2909,68 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W1"/>
+  <dimension ref="A1:L1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>option_id</t>
+          <t>event_key</t>
         </is>
       </c>
       <c r="B1" s="9" t="inlineStr">
         <is>
-          <t>layer</t>
+          <t>ev_src</t>
         </is>
       </c>
       <c r="C1" s="9" t="inlineStr">
         <is>
-          <t>l_label</t>
+          <t>ty</t>
         </is>
       </c>
       <c r="D1" s="9" t="inlineStr">
         <is>
-          <t>iterations</t>
+          <t>event_date</t>
         </is>
       </c>
       <c r="E1" s="9" t="inlineStr">
         <is>
-          <t>lambda_exp</t>
+          <t>n_lives</t>
         </is>
       </c>
       <c r="F1" s="9" t="inlineStr">
         <is>
-          <t>mean_events</t>
+          <t>scheme_id</t>
         </is>
       </c>
       <c r="G1" s="9" t="inlineStr">
         <is>
-          <t>n_hist_events</t>
+          <t>site</t>
         </is>
       </c>
       <c r="H1" s="9" t="inlineStr">
         <is>
-          <t>mean_recovery</t>
+          <t>cause_code</t>
         </is>
       </c>
       <c r="I1" s="9" t="inlineStr">
         <is>
-          <t>sd_recovery</t>
+          <t>loss_raw</t>
         </is>
       </c>
       <c r="J1" s="9" t="inlineStr">
         <is>
-          <t>p_zero</t>
+          <t>trend_f</t>
         </is>
       </c>
       <c r="K1" s="9" t="inlineStr">
         <is>
-          <t>p50</t>
+          <t>loss_adj</t>
         </is>
       </c>
       <c r="L1" s="9" t="inlineStr">
         <is>
-          <t>p90</t>
-        </is>
-      </c>
-      <c r="M1" s="9" t="inlineStr">
-        <is>
-          <t>p95</t>
-        </is>
-      </c>
-      <c r="N1" s="9" t="inlineStr">
-        <is>
-          <t>p99</t>
-        </is>
-      </c>
-      <c r="O1" s="9" t="inlineStr">
-        <is>
-          <t>p995</t>
-        </is>
-      </c>
-      <c r="P1" s="9" t="inlineStr">
-        <is>
-          <t>max_recovery</t>
-        </is>
-      </c>
-      <c r="Q1" s="9" t="inlineStr">
-        <is>
-          <t>mean_reinst_usage</t>
-        </is>
-      </c>
-      <c r="R1" s="9" t="inlineStr">
-        <is>
-          <t>mean_recovery_net_pp</t>
-        </is>
-      </c>
-      <c r="S1" s="9" t="inlineStr">
-        <is>
-          <t>expected_cost_det</t>
-        </is>
-      </c>
-      <c r="T1" s="9" t="inlineStr">
-        <is>
-          <t>credibility_z</t>
-        </is>
-      </c>
-      <c r="U1" s="9" t="inlineStr">
-        <is>
-          <t>expected_loss_blended</t>
-        </is>
-      </c>
-      <c r="V1" s="9" t="inlineStr">
-        <is>
-          <t>expected_loss_pppy</t>
-        </is>
-      </c>
-      <c r="W1" s="9" t="inlineStr">
-        <is>
-          <t>lives_quote_year</t>
+          <t>loss_net_pp</t>
         </is>
       </c>
     </row>
@@ -3025,7 +2986,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:N1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3046,12 +3007,57 @@
       </c>
       <c r="D1" s="9" t="inlineStr">
         <is>
-          <t>q</t>
+          <t>ty</t>
         </is>
       </c>
       <c r="E1" s="9" t="inlineStr">
         <is>
+          <t>exposure_ly_full</t>
+        </is>
+      </c>
+      <c r="F1" s="9" t="inlineStr">
+        <is>
+          <t>n_events</t>
+        </is>
+      </c>
+      <c r="G1" s="9" t="inlineStr">
+        <is>
+          <t>events_per_1000</t>
+        </is>
+      </c>
+      <c r="H1" s="9" t="inlineStr">
+        <is>
+          <t>n_xl</t>
+        </is>
+      </c>
+      <c r="I1" s="9" t="inlineStr">
+        <is>
+          <t>xl</t>
+        </is>
+      </c>
+      <c r="J1" s="9" t="inlineStr">
+        <is>
           <t>recovery</t>
+        </is>
+      </c>
+      <c r="K1" s="9" t="inlineStr">
+        <is>
+          <t>xl_net</t>
+        </is>
+      </c>
+      <c r="L1" s="9" t="inlineStr">
+        <is>
+          <t>recovery_net</t>
+        </is>
+      </c>
+      <c r="M1" s="9" t="inlineStr">
+        <is>
+          <t>bc_pppy</t>
+        </is>
+      </c>
+      <c r="N1" s="9" t="inlineStr">
+        <is>
+          <t>weight</t>
         </is>
       </c>
     </row>
@@ -3067,73 +3073,58 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>ty</t>
+          <t>option_id</t>
         </is>
       </c>
       <c r="B1" s="9" t="inlineStr">
         <is>
-          <t>weight</t>
+          <t>layer</t>
         </is>
       </c>
       <c r="C1" s="9" t="inlineStr">
         <is>
-          <t>exposure_ly_full</t>
+          <t>l_label</t>
         </is>
       </c>
       <c r="D1" s="9" t="inlineStr">
         <is>
-          <t>total_claims</t>
+          <t>n_events</t>
         </is>
       </c>
       <c r="E1" s="9" t="inlineStr">
         <is>
-          <t>n_large</t>
+          <t>n_xl_events</t>
         </is>
       </c>
       <c r="F1" s="9" t="inlineStr">
         <is>
-          <t>large_claims_raw</t>
+          <t>bc_pppy_weighted</t>
         </is>
       </c>
       <c r="G1" s="9" t="inlineStr">
         <is>
-          <t>attritional_raw</t>
+          <t>lives_quote_year</t>
         </is>
       </c>
       <c r="H1" s="9" t="inlineStr">
         <is>
-          <t>months_elapsed</t>
+          <t>expected_cost_det</t>
         </is>
       </c>
       <c r="I1" s="9" t="inlineStr">
         <is>
-          <t>trend_f</t>
+          <t>credibility_z</t>
         </is>
       </c>
       <c r="J1" s="9" t="inlineStr">
         <is>
-          <t>completion_f</t>
-        </is>
-      </c>
-      <c r="K1" s="9" t="inlineStr">
-        <is>
-          <t>attritional_adj</t>
-        </is>
-      </c>
-      <c r="L1" s="9" t="inlineStr">
-        <is>
-          <t>attritional_pppy</t>
-        </is>
-      </c>
-      <c r="M1" s="9" t="inlineStr">
-        <is>
-          <t>t_sl</t>
+          <t>lambda_exp</t>
         </is>
       </c>
     </row>
@@ -3149,118 +3140,63 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V1"/>
+  <dimension ref="A1:K1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>t_sl</t>
+          <t>scenario_name</t>
         </is>
       </c>
       <c r="B1" s="9" t="inlineStr">
         <is>
-          <t>u_fit</t>
+          <t>lives</t>
         </is>
       </c>
       <c r="C1" s="9" t="inlineStr">
         <is>
-          <t>n_years</t>
+          <t>cost_per_life</t>
         </is>
       </c>
       <c r="D1" s="9" t="inlineStr">
         <is>
-          <t>attritional_pppy_weighted</t>
+          <t>return_period_yrs</t>
         </is>
       </c>
       <c r="E1" s="9" t="inlineStr">
         <is>
-          <t>attritional_pppy_mean</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="F1" s="9" t="inlineStr">
         <is>
-          <t>cov_hist</t>
+          <t>loss_net_pp</t>
         </is>
       </c>
       <c r="G1" s="9" t="inlineStr">
         <is>
-          <t>cov_used</t>
+          <t>option_id</t>
         </is>
       </c>
       <c r="H1" s="9" t="inlineStr">
         <is>
-          <t>attritional_dist</t>
+          <t>layer</t>
         </is>
       </c>
       <c r="I1" s="9" t="inlineStr">
         <is>
-          <t>lives_quote_year</t>
+          <t>l_label</t>
         </is>
       </c>
       <c r="J1" s="9" t="inlineStr">
         <is>
-          <t>reference_lives</t>
+          <t>layer_loss</t>
         </is>
       </c>
       <c r="K1" s="9" t="inlineStr">
         <is>
-          <t>incidence_adj</t>
-        </is>
-      </c>
-      <c r="L1" s="9" t="inlineStr">
-        <is>
-          <t>attritional_mean_q</t>
-        </is>
-      </c>
-      <c r="M1" s="9" t="inlineStr">
-        <is>
-          <t>m_ln</t>
-        </is>
-      </c>
-      <c r="N1" s="9" t="inlineStr">
-        <is>
-          <t>sigma_ln</t>
-        </is>
-      </c>
-      <c r="O1" s="9" t="inlineStr">
-        <is>
-          <t>iterations</t>
-        </is>
-      </c>
-      <c r="P1" s="9" t="inlineStr">
-        <is>
-          <t>mean_attritional_sim</t>
-        </is>
-      </c>
-      <c r="Q1" s="9" t="inlineStr">
-        <is>
-          <t>mean_large_sim</t>
-        </is>
-      </c>
-      <c r="R1" s="9" t="inlineStr">
-        <is>
-          <t>mean_gross</t>
-        </is>
-      </c>
-      <c r="S1" s="9" t="inlineStr">
-        <is>
-          <t>sd_gross</t>
-        </is>
-      </c>
-      <c r="T1" s="9" t="inlineStr">
-        <is>
-          <t>budget</t>
-        </is>
-      </c>
-      <c r="U1" s="9" t="inlineStr">
-        <is>
-          <t>budget_source</t>
-        </is>
-      </c>
-      <c r="V1" s="9" t="inlineStr">
-        <is>
-          <t>epi</t>
+          <t>layer_loss_net_pp</t>
         </is>
       </c>
     </row>
@@ -3276,163 +3212,123 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE1"/>
+  <dimension ref="A1:W1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>struct_key</t>
+          <t>option_id</t>
         </is>
       </c>
       <c r="B1" s="9" t="inlineStr">
         <is>
-          <t>cover</t>
+          <t>layer</t>
         </is>
       </c>
       <c r="C1" s="9" t="inlineStr">
         <is>
-          <t>option_id</t>
+          <t>l_label</t>
         </is>
       </c>
       <c r="D1" s="9" t="inlineStr">
         <is>
-          <t>pp_option</t>
+          <t>iterations</t>
         </is>
       </c>
       <c r="E1" s="9" t="inlineStr">
         <is>
-          <t>ev_option</t>
+          <t>lambda_exp</t>
         </is>
       </c>
       <c r="F1" s="9" t="inlineStr">
         <is>
-          <t>sl_option</t>
+          <t>mean_events</t>
         </is>
       </c>
       <c r="G1" s="9" t="inlineStr">
         <is>
-          <t>l_label</t>
+          <t>n_hist_events</t>
         </is>
       </c>
       <c r="H1" s="9" t="inlineStr">
         <is>
-          <t>iterations</t>
+          <t>mean_recovery</t>
         </is>
       </c>
       <c r="I1" s="9" t="inlineStr">
         <is>
-          <t>mean_gross</t>
+          <t>sd_recovery</t>
         </is>
       </c>
       <c r="J1" s="9" t="inlineStr">
         <is>
-          <t>mean_recovery</t>
+          <t>p_zero</t>
         </is>
       </c>
       <c r="K1" s="9" t="inlineStr">
         <is>
-          <t>sd_recovery</t>
+          <t>p50</t>
         </is>
       </c>
       <c r="L1" s="9" t="inlineStr">
         <is>
-          <t>p_zero</t>
+          <t>p90</t>
         </is>
       </c>
       <c r="M1" s="9" t="inlineStr">
         <is>
-          <t>mean_recovery_total</t>
+          <t>p95</t>
         </is>
       </c>
       <c r="N1" s="9" t="inlineStr">
         <is>
-          <t>mean_net</t>
+          <t>p99</t>
         </is>
       </c>
       <c r="O1" s="9" t="inlineStr">
         <is>
-          <t>sd_net</t>
+          <t>p995</t>
         </is>
       </c>
       <c r="P1" s="9" t="inlineStr">
         <is>
-          <t>mean_ru_l1</t>
+          <t>max_recovery</t>
         </is>
       </c>
       <c r="Q1" s="9" t="inlineStr">
         <is>
-          <t>mean_ru_l2</t>
+          <t>mean_reinst_usage</t>
         </is>
       </c>
       <c r="R1" s="9" t="inlineStr">
         <is>
-          <t>mean_ru_ev1</t>
+          <t>mean_recovery_net_pp</t>
         </is>
       </c>
       <c r="S1" s="9" t="inlineStr">
         <is>
-          <t>mean_ru_ev2</t>
+          <t>expected_cost_det</t>
         </is>
       </c>
       <c r="T1" s="9" t="inlineStr">
         <is>
-          <t>sl_basis</t>
+          <t>credibility_z</t>
         </is>
       </c>
       <c r="U1" s="9" t="inlineStr">
         <is>
-          <t>sl_measure</t>
+          <t>expected_loss_blended</t>
         </is>
       </c>
       <c r="V1" s="9" t="inlineStr">
         <is>
-          <t>sl_ap</t>
+          <t>expected_loss_pppy</t>
         </is>
       </c>
       <c r="W1" s="9" t="inlineStr">
         <is>
-          <t>sl_limit</t>
-        </is>
-      </c>
-      <c r="X1" s="9" t="inlineStr">
-        <is>
-          <t>ap_amount</t>
-        </is>
-      </c>
-      <c r="Y1" s="9" t="inlineStr">
-        <is>
-          <t>limit_amount</t>
-        </is>
-      </c>
-      <c r="Z1" s="9" t="inlineStr">
-        <is>
-          <t>ap_pct_budget</t>
-        </is>
-      </c>
-      <c r="AA1" s="9" t="inlineStr">
-        <is>
-          <t>limit_pct_budget</t>
-        </is>
-      </c>
-      <c r="AB1" s="9" t="inlineStr">
-        <is>
-          <t>ap_pct_epi</t>
-        </is>
-      </c>
-      <c r="AC1" s="9" t="inlineStr">
-        <is>
-          <t>limit_pct_epi</t>
-        </is>
-      </c>
-      <c r="AD1" s="9" t="inlineStr">
-        <is>
-          <t>budget</t>
-        </is>
-      </c>
-      <c r="AE1" s="9" t="inlineStr">
-        <is>
-          <t>epi</t>
+          <t>lives_quote_year</t>
         </is>
       </c>
     </row>
@@ -4969,81 +4865,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O1"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>struct_key</t>
+          <t>option_id</t>
         </is>
       </c>
       <c r="B1" s="9" t="inlineStr">
         <is>
-          <t>cover</t>
+          <t>layer</t>
         </is>
       </c>
       <c r="C1" s="9" t="inlineStr">
         <is>
-          <t>option_id</t>
+          <t>l_label</t>
         </is>
       </c>
       <c r="D1" s="9" t="inlineStr">
         <is>
-          <t>pp_option</t>
+          <t>q</t>
         </is>
       </c>
       <c r="E1" s="9" t="inlineStr">
-        <is>
-          <t>ev_option</t>
-        </is>
-      </c>
-      <c r="F1" s="9" t="inlineStr">
-        <is>
-          <t>sl_option</t>
-        </is>
-      </c>
-      <c r="G1" s="9" t="inlineStr">
-        <is>
-          <t>l_label</t>
-        </is>
-      </c>
-      <c r="H1" s="9" t="inlineStr">
-        <is>
-          <t>q</t>
-        </is>
-      </c>
-      <c r="I1" s="9" t="inlineStr">
-        <is>
-          <t>qm</t>
-        </is>
-      </c>
-      <c r="J1" s="9" t="inlineStr">
-        <is>
-          <t>net_claims</t>
-        </is>
-      </c>
-      <c r="K1" s="9" t="inlineStr">
-        <is>
-          <t>ru_l1_at_q</t>
-        </is>
-      </c>
-      <c r="L1" s="9" t="inlineStr">
-        <is>
-          <t>ru_l2_at_q</t>
-        </is>
-      </c>
-      <c r="M1" s="9" t="inlineStr">
-        <is>
-          <t>ru_ev1_at_q</t>
-        </is>
-      </c>
-      <c r="N1" s="9" t="inlineStr">
-        <is>
-          <t>ru_ev2_at_q</t>
-        </is>
-      </c>
-      <c r="O1" s="9" t="inlineStr">
         <is>
           <t>recovery</t>
         </is>
@@ -5061,58 +4907,73 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:M1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>cover</t>
+          <t>ty</t>
         </is>
       </c>
       <c r="B1" s="9" t="inlineStr">
         <is>
-          <t>option_id</t>
+          <t>weight</t>
         </is>
       </c>
       <c r="C1" s="9" t="inlineStr">
         <is>
-          <t>layer</t>
+          <t>exposure_ly_full</t>
         </is>
       </c>
       <c r="D1" s="9" t="inlineStr">
         <is>
-          <t>l_label</t>
+          <t>total_claims</t>
         </is>
       </c>
       <c r="E1" s="9" t="inlineStr">
         <is>
-          <t>ap</t>
+          <t>n_large</t>
         </is>
       </c>
       <c r="F1" s="9" t="inlineStr">
         <is>
-          <t>share_exposed</t>
+          <t>large_claims_raw</t>
         </is>
       </c>
       <c r="G1" s="9" t="inlineStr">
         <is>
-          <t>exposed_lives</t>
+          <t>attritional_raw</t>
         </is>
       </c>
       <c r="H1" s="9" t="inlineStr">
         <is>
-          <t>lives_quote_year</t>
+          <t>months_elapsed</t>
         </is>
       </c>
       <c r="I1" s="9" t="inlineStr">
         <is>
-          <t>reference_lives</t>
+          <t>trend_f</t>
         </is>
       </c>
       <c r="J1" s="9" t="inlineStr">
         <is>
-          <t>basis_note</t>
+          <t>completion_f</t>
+        </is>
+      </c>
+      <c r="K1" s="9" t="inlineStr">
+        <is>
+          <t>attritional_adj</t>
+        </is>
+      </c>
+      <c r="L1" s="9" t="inlineStr">
+        <is>
+          <t>attritional_pppy</t>
+        </is>
+      </c>
+      <c r="M1" s="9" t="inlineStr">
+        <is>
+          <t>t_sl</t>
         </is>
       </c>
     </row>
@@ -5128,73 +4989,118 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:V1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>cover</t>
+          <t>t_sl</t>
         </is>
       </c>
       <c r="B1" s="9" t="inlineStr">
         <is>
-          <t>layer</t>
+          <t>u_fit</t>
         </is>
       </c>
       <c r="C1" s="9" t="inlineStr">
         <is>
-          <t>ap</t>
+          <t>n_years</t>
         </is>
       </c>
       <c r="D1" s="9" t="inlineStr">
         <is>
-          <t>limit</t>
+          <t>attritional_pppy_weighted</t>
         </is>
       </c>
       <c r="E1" s="9" t="inlineStr">
         <is>
-          <t>rate_basis</t>
+          <t>attritional_pppy_mean</t>
         </is>
       </c>
       <c r="F1" s="9" t="inlineStr">
         <is>
-          <t>rate</t>
+          <t>cov_hist</t>
         </is>
       </c>
       <c r="G1" s="9" t="inlineStr">
         <is>
-          <t>premium</t>
+          <t>cov_used</t>
         </is>
       </c>
       <c r="H1" s="9" t="inlineStr">
         <is>
-          <t>matched_option</t>
+          <t>attritional_dist</t>
         </is>
       </c>
       <c r="I1" s="9" t="inlineStr">
         <is>
-          <t>lev_trend_used</t>
+          <t>lives_quote_year</t>
         </is>
       </c>
       <c r="J1" s="9" t="inlineStr">
         <is>
-          <t>lives_quote_year</t>
+          <t>reference_lives</t>
         </is>
       </c>
       <c r="K1" s="9" t="inlineStr">
         <is>
+          <t>incidence_adj</t>
+        </is>
+      </c>
+      <c r="L1" s="9" t="inlineStr">
+        <is>
+          <t>attritional_mean_q</t>
+        </is>
+      </c>
+      <c r="M1" s="9" t="inlineStr">
+        <is>
+          <t>m_ln</t>
+        </is>
+      </c>
+      <c r="N1" s="9" t="inlineStr">
+        <is>
+          <t>sigma_ln</t>
+        </is>
+      </c>
+      <c r="O1" s="9" t="inlineStr">
+        <is>
+          <t>iterations</t>
+        </is>
+      </c>
+      <c r="P1" s="9" t="inlineStr">
+        <is>
+          <t>mean_attritional_sim</t>
+        </is>
+      </c>
+      <c r="Q1" s="9" t="inlineStr">
+        <is>
+          <t>mean_large_sim</t>
+        </is>
+      </c>
+      <c r="R1" s="9" t="inlineStr">
+        <is>
+          <t>mean_gross</t>
+        </is>
+      </c>
+      <c r="S1" s="9" t="inlineStr">
+        <is>
+          <t>sd_gross</t>
+        </is>
+      </c>
+      <c r="T1" s="9" t="inlineStr">
+        <is>
+          <t>budget</t>
+        </is>
+      </c>
+      <c r="U1" s="9" t="inlineStr">
+        <is>
+          <t>budget_source</t>
+        </is>
+      </c>
+      <c r="V1" s="9" t="inlineStr">
+        <is>
           <t>epi</t>
-        </is>
-      </c>
-      <c r="L1" s="9" t="inlineStr">
-        <is>
-          <t>expiring_premium_q</t>
-        </is>
-      </c>
-      <c r="M1" s="9" t="inlineStr">
-        <is>
-          <t>expiring_premium_trended</t>
         </is>
       </c>
     </row>
@@ -5210,58 +5116,163 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:AE1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
+          <t>struct_key</t>
+        </is>
+      </c>
+      <c r="B1" s="9" t="inlineStr">
+        <is>
           <t>cover</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
-        <is>
-          <t>layer</t>
-        </is>
-      </c>
       <c r="C1" s="9" t="inlineStr">
         <is>
-          <t>matched_option</t>
+          <t>option_id</t>
         </is>
       </c>
       <c r="D1" s="9" t="inlineStr">
         <is>
-          <t>ty</t>
+          <t>pp_option</t>
         </is>
       </c>
       <c r="E1" s="9" t="inlineStr">
         <is>
-          <t>exposure_ly_full</t>
+          <t>ev_option</t>
         </is>
       </c>
       <c r="F1" s="9" t="inlineStr">
         <is>
-          <t>exposure_prem_full</t>
+          <t>sl_option</t>
         </is>
       </c>
       <c r="G1" s="9" t="inlineStr">
         <is>
-          <t>asif_recovery</t>
+          <t>l_label</t>
         </is>
       </c>
       <c r="H1" s="9" t="inlineStr">
         <is>
-          <t>asif_premium</t>
+          <t>iterations</t>
         </is>
       </c>
       <c r="I1" s="9" t="inlineStr">
         <is>
-          <t>premium_year_level</t>
+          <t>mean_gross</t>
         </is>
       </c>
       <c r="J1" s="9" t="inlineStr">
         <is>
-          <t>actual_recovery</t>
+          <t>mean_recovery</t>
+        </is>
+      </c>
+      <c r="K1" s="9" t="inlineStr">
+        <is>
+          <t>sd_recovery</t>
+        </is>
+      </c>
+      <c r="L1" s="9" t="inlineStr">
+        <is>
+          <t>p_zero</t>
+        </is>
+      </c>
+      <c r="M1" s="9" t="inlineStr">
+        <is>
+          <t>mean_recovery_total</t>
+        </is>
+      </c>
+      <c r="N1" s="9" t="inlineStr">
+        <is>
+          <t>mean_net</t>
+        </is>
+      </c>
+      <c r="O1" s="9" t="inlineStr">
+        <is>
+          <t>sd_net</t>
+        </is>
+      </c>
+      <c r="P1" s="9" t="inlineStr">
+        <is>
+          <t>mean_ru_l1</t>
+        </is>
+      </c>
+      <c r="Q1" s="9" t="inlineStr">
+        <is>
+          <t>mean_ru_l2</t>
+        </is>
+      </c>
+      <c r="R1" s="9" t="inlineStr">
+        <is>
+          <t>mean_ru_ev1</t>
+        </is>
+      </c>
+      <c r="S1" s="9" t="inlineStr">
+        <is>
+          <t>mean_ru_ev2</t>
+        </is>
+      </c>
+      <c r="T1" s="9" t="inlineStr">
+        <is>
+          <t>sl_basis</t>
+        </is>
+      </c>
+      <c r="U1" s="9" t="inlineStr">
+        <is>
+          <t>sl_measure</t>
+        </is>
+      </c>
+      <c r="V1" s="9" t="inlineStr">
+        <is>
+          <t>sl_ap</t>
+        </is>
+      </c>
+      <c r="W1" s="9" t="inlineStr">
+        <is>
+          <t>sl_limit</t>
+        </is>
+      </c>
+      <c r="X1" s="9" t="inlineStr">
+        <is>
+          <t>ap_amount</t>
+        </is>
+      </c>
+      <c r="Y1" s="9" t="inlineStr">
+        <is>
+          <t>limit_amount</t>
+        </is>
+      </c>
+      <c r="Z1" s="9" t="inlineStr">
+        <is>
+          <t>ap_pct_budget</t>
+        </is>
+      </c>
+      <c r="AA1" s="9" t="inlineStr">
+        <is>
+          <t>limit_pct_budget</t>
+        </is>
+      </c>
+      <c r="AB1" s="9" t="inlineStr">
+        <is>
+          <t>ap_pct_epi</t>
+        </is>
+      </c>
+      <c r="AC1" s="9" t="inlineStr">
+        <is>
+          <t>limit_pct_epi</t>
+        </is>
+      </c>
+      <c r="AD1" s="9" t="inlineStr">
+        <is>
+          <t>budget</t>
+        </is>
+      </c>
+      <c r="AE1" s="9" t="inlineStr">
+        <is>
+          <t>epi</t>
         </is>
       </c>
     </row>
@@ -5271,6 +5282,314 @@
 </file>
 
 <file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00A6A6A6"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>struct_key</t>
+        </is>
+      </c>
+      <c r="B1" s="9" t="inlineStr">
+        <is>
+          <t>cover</t>
+        </is>
+      </c>
+      <c r="C1" s="9" t="inlineStr">
+        <is>
+          <t>option_id</t>
+        </is>
+      </c>
+      <c r="D1" s="9" t="inlineStr">
+        <is>
+          <t>pp_option</t>
+        </is>
+      </c>
+      <c r="E1" s="9" t="inlineStr">
+        <is>
+          <t>ev_option</t>
+        </is>
+      </c>
+      <c r="F1" s="9" t="inlineStr">
+        <is>
+          <t>sl_option</t>
+        </is>
+      </c>
+      <c r="G1" s="9" t="inlineStr">
+        <is>
+          <t>l_label</t>
+        </is>
+      </c>
+      <c r="H1" s="9" t="inlineStr">
+        <is>
+          <t>q</t>
+        </is>
+      </c>
+      <c r="I1" s="9" t="inlineStr">
+        <is>
+          <t>qm</t>
+        </is>
+      </c>
+      <c r="J1" s="9" t="inlineStr">
+        <is>
+          <t>net_claims</t>
+        </is>
+      </c>
+      <c r="K1" s="9" t="inlineStr">
+        <is>
+          <t>ru_l1_at_q</t>
+        </is>
+      </c>
+      <c r="L1" s="9" t="inlineStr">
+        <is>
+          <t>ru_l2_at_q</t>
+        </is>
+      </c>
+      <c r="M1" s="9" t="inlineStr">
+        <is>
+          <t>ru_ev1_at_q</t>
+        </is>
+      </c>
+      <c r="N1" s="9" t="inlineStr">
+        <is>
+          <t>ru_ev2_at_q</t>
+        </is>
+      </c>
+      <c r="O1" s="9" t="inlineStr">
+        <is>
+          <t>recovery</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00A6A6A6"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>cover</t>
+        </is>
+      </c>
+      <c r="B1" s="9" t="inlineStr">
+        <is>
+          <t>option_id</t>
+        </is>
+      </c>
+      <c r="C1" s="9" t="inlineStr">
+        <is>
+          <t>layer</t>
+        </is>
+      </c>
+      <c r="D1" s="9" t="inlineStr">
+        <is>
+          <t>l_label</t>
+        </is>
+      </c>
+      <c r="E1" s="9" t="inlineStr">
+        <is>
+          <t>ap</t>
+        </is>
+      </c>
+      <c r="F1" s="9" t="inlineStr">
+        <is>
+          <t>share_exposed</t>
+        </is>
+      </c>
+      <c r="G1" s="9" t="inlineStr">
+        <is>
+          <t>exposed_lives</t>
+        </is>
+      </c>
+      <c r="H1" s="9" t="inlineStr">
+        <is>
+          <t>lives_quote_year</t>
+        </is>
+      </c>
+      <c r="I1" s="9" t="inlineStr">
+        <is>
+          <t>reference_lives</t>
+        </is>
+      </c>
+      <c r="J1" s="9" t="inlineStr">
+        <is>
+          <t>basis_note</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00A6A6A6"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>cover</t>
+        </is>
+      </c>
+      <c r="B1" s="9" t="inlineStr">
+        <is>
+          <t>layer</t>
+        </is>
+      </c>
+      <c r="C1" s="9" t="inlineStr">
+        <is>
+          <t>ap</t>
+        </is>
+      </c>
+      <c r="D1" s="9" t="inlineStr">
+        <is>
+          <t>limit</t>
+        </is>
+      </c>
+      <c r="E1" s="9" t="inlineStr">
+        <is>
+          <t>rate_basis</t>
+        </is>
+      </c>
+      <c r="F1" s="9" t="inlineStr">
+        <is>
+          <t>rate</t>
+        </is>
+      </c>
+      <c r="G1" s="9" t="inlineStr">
+        <is>
+          <t>premium</t>
+        </is>
+      </c>
+      <c r="H1" s="9" t="inlineStr">
+        <is>
+          <t>matched_option</t>
+        </is>
+      </c>
+      <c r="I1" s="9" t="inlineStr">
+        <is>
+          <t>lev_trend_used</t>
+        </is>
+      </c>
+      <c r="J1" s="9" t="inlineStr">
+        <is>
+          <t>lives_quote_year</t>
+        </is>
+      </c>
+      <c r="K1" s="9" t="inlineStr">
+        <is>
+          <t>epi</t>
+        </is>
+      </c>
+      <c r="L1" s="9" t="inlineStr">
+        <is>
+          <t>expiring_premium_q</t>
+        </is>
+      </c>
+      <c r="M1" s="9" t="inlineStr">
+        <is>
+          <t>expiring_premium_trended</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00A6A6A6"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>cover</t>
+        </is>
+      </c>
+      <c r="B1" s="9" t="inlineStr">
+        <is>
+          <t>layer</t>
+        </is>
+      </c>
+      <c r="C1" s="9" t="inlineStr">
+        <is>
+          <t>matched_option</t>
+        </is>
+      </c>
+      <c r="D1" s="9" t="inlineStr">
+        <is>
+          <t>ty</t>
+        </is>
+      </c>
+      <c r="E1" s="9" t="inlineStr">
+        <is>
+          <t>exposure_ly_full</t>
+        </is>
+      </c>
+      <c r="F1" s="9" t="inlineStr">
+        <is>
+          <t>exposure_prem_full</t>
+        </is>
+      </c>
+      <c r="G1" s="9" t="inlineStr">
+        <is>
+          <t>asif_recovery</t>
+        </is>
+      </c>
+      <c r="H1" s="9" t="inlineStr">
+        <is>
+          <t>asif_premium</t>
+        </is>
+      </c>
+      <c r="I1" s="9" t="inlineStr">
+        <is>
+          <t>premium_year_level</t>
+        </is>
+      </c>
+      <c r="J1" s="9" t="inlineStr">
+        <is>
+          <t>actual_recovery</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00A6A6A6"/>
@@ -8379,6 +8698,2554 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:N75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Severity fit above u (stage 04a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Candidates fitted to the trended, completed, capped claims above u: left-truncated at u, censored at the benefit / policy limits. The simulation uses the selected one when severity_source = PYTHON (Control).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>Threshold u</t>
+        </is>
+      </c>
+      <c r="B4" s="26">
+        <f>IFERROR(INDEX(fc_u_fit,1),"")</f>
+        <v/>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>Uncensored units</t>
+        </is>
+      </c>
+      <c r="D4" s="32">
+        <f>IFERROR(INDEX(fc_n_uncensored,1),"")</f>
+        <v/>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>Largest observed</t>
+        </is>
+      </c>
+      <c r="F4" s="26">
+        <f>IFERROR(INDEX(fc_max_observed,1),"")</f>
+        <v/>
+      </c>
+      <c r="G4" s="9" t="inlineStr">
+        <is>
+          <t>Used by the simulation</t>
+        </is>
+      </c>
+      <c r="H4" s="9">
+        <f>IFERROR(INDEX(ps_sev_dist,1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="42" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Distribution</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Parameter 1</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Parameter 2</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>Log-likelihood</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>AIC</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>BIC</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>KS</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>Rank (AIC)</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>Boundary fit</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>Selected</t>
+        </is>
+      </c>
+      <c r="M6" s="5" t="inlineStr">
+        <is>
+          <t>Mean excess ratio min</t>
+        </is>
+      </c>
+      <c r="N6" s="5" t="inlineStr">
+        <is>
+          <t>Mean excess ratio max</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6">
+        <f>IFERROR(INDEX(fc_dist,1)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="B7" s="6">
+        <f>IFERROR(INDEX(fc_p1_name,1)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="C7" s="46">
+        <f>IFERROR(IF(INDEX(fc_p1,1)="","",INDEX(fc_p1,1)),"")</f>
+        <v/>
+      </c>
+      <c r="D7" s="6">
+        <f>IFERROR(INDEX(fc_p2_name,1)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="E7" s="47">
+        <f>IFERROR(IF(INDEX(fc_p2,1)="","",INDEX(fc_p2,1)),"")</f>
+        <v/>
+      </c>
+      <c r="F7" s="30">
+        <f>IFERROR(IF(INDEX(fc_loglik,1)="","",INDEX(fc_loglik,1)),"")</f>
+        <v/>
+      </c>
+      <c r="G7" s="30">
+        <f>IFERROR(IF(INDEX(fc_aic,1)="","",INDEX(fc_aic,1)),"")</f>
+        <v/>
+      </c>
+      <c r="H7" s="30">
+        <f>IFERROR(IF(INDEX(fc_bic,1)="","",INDEX(fc_bic,1)),"")</f>
+        <v/>
+      </c>
+      <c r="I7" s="46">
+        <f>IFERROR(IF(INDEX(fc_ks,1)="","",INDEX(fc_ks,1)),"")</f>
+        <v/>
+      </c>
+      <c r="J7" s="44">
+        <f>IFERROR(IF(INDEX(fc_rank_aic,1)="","",INDEX(fc_rank_aic,1)),"")</f>
+        <v/>
+      </c>
+      <c r="K7" s="44">
+        <f>IFERROR(IF(INDEX(fc_boundary,1)="","",INDEX(fc_boundary,1)),"")</f>
+        <v/>
+      </c>
+      <c r="L7" s="44">
+        <f>IFERROR(IF(INDEX(fc_selected,1)="","",INDEX(fc_selected,1)),"")</f>
+        <v/>
+      </c>
+      <c r="M7" s="29">
+        <f>IFERROR(IF(INDEX(fc_me_ratio_min,1)="","",INDEX(fc_me_ratio_min,1)),"")</f>
+        <v/>
+      </c>
+      <c r="N7" s="29">
+        <f>IFERROR(IF(INDEX(fc_me_ratio_max,1)="","",INDEX(fc_me_ratio_max,1)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6">
+        <f>IFERROR(INDEX(fc_dist,2)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="B8" s="6">
+        <f>IFERROR(INDEX(fc_p1_name,2)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="C8" s="46">
+        <f>IFERROR(IF(INDEX(fc_p1,2)="","",INDEX(fc_p1,2)),"")</f>
+        <v/>
+      </c>
+      <c r="D8" s="6">
+        <f>IFERROR(INDEX(fc_p2_name,2)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="E8" s="47">
+        <f>IFERROR(IF(INDEX(fc_p2,2)="","",INDEX(fc_p2,2)),"")</f>
+        <v/>
+      </c>
+      <c r="F8" s="30">
+        <f>IFERROR(IF(INDEX(fc_loglik,2)="","",INDEX(fc_loglik,2)),"")</f>
+        <v/>
+      </c>
+      <c r="G8" s="30">
+        <f>IFERROR(IF(INDEX(fc_aic,2)="","",INDEX(fc_aic,2)),"")</f>
+        <v/>
+      </c>
+      <c r="H8" s="30">
+        <f>IFERROR(IF(INDEX(fc_bic,2)="","",INDEX(fc_bic,2)),"")</f>
+        <v/>
+      </c>
+      <c r="I8" s="46">
+        <f>IFERROR(IF(INDEX(fc_ks,2)="","",INDEX(fc_ks,2)),"")</f>
+        <v/>
+      </c>
+      <c r="J8" s="44">
+        <f>IFERROR(IF(INDEX(fc_rank_aic,2)="","",INDEX(fc_rank_aic,2)),"")</f>
+        <v/>
+      </c>
+      <c r="K8" s="44">
+        <f>IFERROR(IF(INDEX(fc_boundary,2)="","",INDEX(fc_boundary,2)),"")</f>
+        <v/>
+      </c>
+      <c r="L8" s="44">
+        <f>IFERROR(IF(INDEX(fc_selected,2)="","",INDEX(fc_selected,2)),"")</f>
+        <v/>
+      </c>
+      <c r="M8" s="29">
+        <f>IFERROR(IF(INDEX(fc_me_ratio_min,2)="","",INDEX(fc_me_ratio_min,2)),"")</f>
+        <v/>
+      </c>
+      <c r="N8" s="29">
+        <f>IFERROR(IF(INDEX(fc_me_ratio_max,2)="","",INDEX(fc_me_ratio_max,2)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6">
+        <f>IFERROR(INDEX(fc_dist,3)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="B9" s="6">
+        <f>IFERROR(INDEX(fc_p1_name,3)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="C9" s="46">
+        <f>IFERROR(IF(INDEX(fc_p1,3)="","",INDEX(fc_p1,3)),"")</f>
+        <v/>
+      </c>
+      <c r="D9" s="6">
+        <f>IFERROR(INDEX(fc_p2_name,3)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="E9" s="47">
+        <f>IFERROR(IF(INDEX(fc_p2,3)="","",INDEX(fc_p2,3)),"")</f>
+        <v/>
+      </c>
+      <c r="F9" s="30">
+        <f>IFERROR(IF(INDEX(fc_loglik,3)="","",INDEX(fc_loglik,3)),"")</f>
+        <v/>
+      </c>
+      <c r="G9" s="30">
+        <f>IFERROR(IF(INDEX(fc_aic,3)="","",INDEX(fc_aic,3)),"")</f>
+        <v/>
+      </c>
+      <c r="H9" s="30">
+        <f>IFERROR(IF(INDEX(fc_bic,3)="","",INDEX(fc_bic,3)),"")</f>
+        <v/>
+      </c>
+      <c r="I9" s="46">
+        <f>IFERROR(IF(INDEX(fc_ks,3)="","",INDEX(fc_ks,3)),"")</f>
+        <v/>
+      </c>
+      <c r="J9" s="44">
+        <f>IFERROR(IF(INDEX(fc_rank_aic,3)="","",INDEX(fc_rank_aic,3)),"")</f>
+        <v/>
+      </c>
+      <c r="K9" s="44">
+        <f>IFERROR(IF(INDEX(fc_boundary,3)="","",INDEX(fc_boundary,3)),"")</f>
+        <v/>
+      </c>
+      <c r="L9" s="44">
+        <f>IFERROR(IF(INDEX(fc_selected,3)="","",INDEX(fc_selected,3)),"")</f>
+        <v/>
+      </c>
+      <c r="M9" s="29">
+        <f>IFERROR(IF(INDEX(fc_me_ratio_min,3)="","",INDEX(fc_me_ratio_min,3)),"")</f>
+        <v/>
+      </c>
+      <c r="N9" s="29">
+        <f>IFERROR(IF(INDEX(fc_me_ratio_max,3)="","",INDEX(fc_me_ratio_max,3)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6">
+        <f>IFERROR(INDEX(fc_dist,4)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="B10" s="6">
+        <f>IFERROR(INDEX(fc_p1_name,4)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="C10" s="46">
+        <f>IFERROR(IF(INDEX(fc_p1,4)="","",INDEX(fc_p1,4)),"")</f>
+        <v/>
+      </c>
+      <c r="D10" s="6">
+        <f>IFERROR(INDEX(fc_p2_name,4)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="E10" s="47">
+        <f>IFERROR(IF(INDEX(fc_p2,4)="","",INDEX(fc_p2,4)),"")</f>
+        <v/>
+      </c>
+      <c r="F10" s="30">
+        <f>IFERROR(IF(INDEX(fc_loglik,4)="","",INDEX(fc_loglik,4)),"")</f>
+        <v/>
+      </c>
+      <c r="G10" s="30">
+        <f>IFERROR(IF(INDEX(fc_aic,4)="","",INDEX(fc_aic,4)),"")</f>
+        <v/>
+      </c>
+      <c r="H10" s="30">
+        <f>IFERROR(IF(INDEX(fc_bic,4)="","",INDEX(fc_bic,4)),"")</f>
+        <v/>
+      </c>
+      <c r="I10" s="46">
+        <f>IFERROR(IF(INDEX(fc_ks,4)="","",INDEX(fc_ks,4)),"")</f>
+        <v/>
+      </c>
+      <c r="J10" s="44">
+        <f>IFERROR(IF(INDEX(fc_rank_aic,4)="","",INDEX(fc_rank_aic,4)),"")</f>
+        <v/>
+      </c>
+      <c r="K10" s="44">
+        <f>IFERROR(IF(INDEX(fc_boundary,4)="","",INDEX(fc_boundary,4)),"")</f>
+        <v/>
+      </c>
+      <c r="L10" s="44">
+        <f>IFERROR(IF(INDEX(fc_selected,4)="","",INDEX(fc_selected,4)),"")</f>
+        <v/>
+      </c>
+      <c r="M10" s="29">
+        <f>IFERROR(IF(INDEX(fc_me_ratio_min,4)="","",INDEX(fc_me_ratio_min,4)),"")</f>
+        <v/>
+      </c>
+      <c r="N10" s="29">
+        <f>IFERROR(IF(INDEX(fc_me_ratio_max,4)="","",INDEX(fc_me_ratio_max,4)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6">
+        <f>IFERROR(INDEX(fc_dist,5)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="B11" s="6">
+        <f>IFERROR(INDEX(fc_p1_name,5)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="C11" s="46">
+        <f>IFERROR(IF(INDEX(fc_p1,5)="","",INDEX(fc_p1,5)),"")</f>
+        <v/>
+      </c>
+      <c r="D11" s="6">
+        <f>IFERROR(INDEX(fc_p2_name,5)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="E11" s="47">
+        <f>IFERROR(IF(INDEX(fc_p2,5)="","",INDEX(fc_p2,5)),"")</f>
+        <v/>
+      </c>
+      <c r="F11" s="30">
+        <f>IFERROR(IF(INDEX(fc_loglik,5)="","",INDEX(fc_loglik,5)),"")</f>
+        <v/>
+      </c>
+      <c r="G11" s="30">
+        <f>IFERROR(IF(INDEX(fc_aic,5)="","",INDEX(fc_aic,5)),"")</f>
+        <v/>
+      </c>
+      <c r="H11" s="30">
+        <f>IFERROR(IF(INDEX(fc_bic,5)="","",INDEX(fc_bic,5)),"")</f>
+        <v/>
+      </c>
+      <c r="I11" s="46">
+        <f>IFERROR(IF(INDEX(fc_ks,5)="","",INDEX(fc_ks,5)),"")</f>
+        <v/>
+      </c>
+      <c r="J11" s="44">
+        <f>IFERROR(IF(INDEX(fc_rank_aic,5)="","",INDEX(fc_rank_aic,5)),"")</f>
+        <v/>
+      </c>
+      <c r="K11" s="44">
+        <f>IFERROR(IF(INDEX(fc_boundary,5)="","",INDEX(fc_boundary,5)),"")</f>
+        <v/>
+      </c>
+      <c r="L11" s="44">
+        <f>IFERROR(IF(INDEX(fc_selected,5)="","",INDEX(fc_selected,5)),"")</f>
+        <v/>
+      </c>
+      <c r="M11" s="29">
+        <f>IFERROR(IF(INDEX(fc_me_ratio_min,5)="","",INDEX(fc_me_ratio_min,5)),"")</f>
+        <v/>
+      </c>
+      <c r="N11" s="29">
+        <f>IFERROR(IF(INDEX(fc_me_ratio_max,5)="","",INDEX(fc_me_ratio_max,5)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>AIC = 2k - 2 log L; BIC = k ln n - 2 log L; KS = largest distance between the fitted conditional survival and the Kaplan-Meier estimate. Boundary fit: the optimum runs to an extreme parameter (no proper maximum above u); never selected automatically. Selection: fit_selected, else the lowest AIC. Mean excess ratio: fitted / empirical E[X - AP | X &gt; AP] (caps and the largest observed claim applied), 0.8-1.25 expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="42" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Distribution</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Units above AP</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>Mean excess (data)</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>Mean excess (fitted)</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>Ratio</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>Distribution</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>Threshold</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>Label</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="inlineStr">
+        <is>
+          <t>Survival (Kaplan-Meier)</t>
+        </is>
+      </c>
+      <c r="L15" s="5" t="inlineStr">
+        <is>
+          <t>Survival (fitted)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6">
+        <f>IFERROR(INDEX(fm_dist,1)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="B16" s="26">
+        <f>IFERROR(IF(INDEX(fm_ap,1)="","",INDEX(fm_ap,1)),"")</f>
+        <v/>
+      </c>
+      <c r="C16" s="32">
+        <f>IFERROR(IF(INDEX(fm_n_above,1)="","",INDEX(fm_n_above,1)),"")</f>
+        <v/>
+      </c>
+      <c r="D16" s="26">
+        <f>IFERROR(IF(INDEX(fm_mean_excess_empirical,1)="","",INDEX(fm_mean_excess_empirical,1)),"")</f>
+        <v/>
+      </c>
+      <c r="E16" s="26">
+        <f>IFERROR(IF(INDEX(fm_mean_excess_fitted,1)="","",INDEX(fm_mean_excess_fitted,1)),"")</f>
+        <v/>
+      </c>
+      <c r="F16" s="29">
+        <f>IFERROR(IF(INDEX(fm_ratio,1)="","",INDEX(fm_ratio,1)),"")</f>
+        <v/>
+      </c>
+      <c r="H16" s="6">
+        <f>IFERROR(INDEX(fv_dist,1)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="I16" s="26">
+        <f>IFERROR(IF(INDEX(fv_t,1)="","",INDEX(fv_t,1)),"")</f>
+        <v/>
+      </c>
+      <c r="J16" s="6">
+        <f>IFERROR(INDEX(fv_t_label,1)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="K16" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_km,1)="","",INDEX(fv_s_km,1)),"")</f>
+        <v/>
+      </c>
+      <c r="L16" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_fitted,1)="","",INDEX(fv_s_fitted,1)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6">
+        <f>IFERROR(INDEX(fm_dist,2)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="B17" s="26">
+        <f>IFERROR(IF(INDEX(fm_ap,2)="","",INDEX(fm_ap,2)),"")</f>
+        <v/>
+      </c>
+      <c r="C17" s="32">
+        <f>IFERROR(IF(INDEX(fm_n_above,2)="","",INDEX(fm_n_above,2)),"")</f>
+        <v/>
+      </c>
+      <c r="D17" s="26">
+        <f>IFERROR(IF(INDEX(fm_mean_excess_empirical,2)="","",INDEX(fm_mean_excess_empirical,2)),"")</f>
+        <v/>
+      </c>
+      <c r="E17" s="26">
+        <f>IFERROR(IF(INDEX(fm_mean_excess_fitted,2)="","",INDEX(fm_mean_excess_fitted,2)),"")</f>
+        <v/>
+      </c>
+      <c r="F17" s="29">
+        <f>IFERROR(IF(INDEX(fm_ratio,2)="","",INDEX(fm_ratio,2)),"")</f>
+        <v/>
+      </c>
+      <c r="H17" s="6">
+        <f>IFERROR(INDEX(fv_dist,2)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="I17" s="26">
+        <f>IFERROR(IF(INDEX(fv_t,2)="","",INDEX(fv_t,2)),"")</f>
+        <v/>
+      </c>
+      <c r="J17" s="6">
+        <f>IFERROR(INDEX(fv_t_label,2)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="K17" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_km,2)="","",INDEX(fv_s_km,2)),"")</f>
+        <v/>
+      </c>
+      <c r="L17" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_fitted,2)="","",INDEX(fv_s_fitted,2)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6">
+        <f>IFERROR(INDEX(fm_dist,3)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="B18" s="26">
+        <f>IFERROR(IF(INDEX(fm_ap,3)="","",INDEX(fm_ap,3)),"")</f>
+        <v/>
+      </c>
+      <c r="C18" s="32">
+        <f>IFERROR(IF(INDEX(fm_n_above,3)="","",INDEX(fm_n_above,3)),"")</f>
+        <v/>
+      </c>
+      <c r="D18" s="26">
+        <f>IFERROR(IF(INDEX(fm_mean_excess_empirical,3)="","",INDEX(fm_mean_excess_empirical,3)),"")</f>
+        <v/>
+      </c>
+      <c r="E18" s="26">
+        <f>IFERROR(IF(INDEX(fm_mean_excess_fitted,3)="","",INDEX(fm_mean_excess_fitted,3)),"")</f>
+        <v/>
+      </c>
+      <c r="F18" s="29">
+        <f>IFERROR(IF(INDEX(fm_ratio,3)="","",INDEX(fm_ratio,3)),"")</f>
+        <v/>
+      </c>
+      <c r="H18" s="6">
+        <f>IFERROR(INDEX(fv_dist,3)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="I18" s="26">
+        <f>IFERROR(IF(INDEX(fv_t,3)="","",INDEX(fv_t,3)),"")</f>
+        <v/>
+      </c>
+      <c r="J18" s="6">
+        <f>IFERROR(INDEX(fv_t_label,3)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="K18" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_km,3)="","",INDEX(fv_s_km,3)),"")</f>
+        <v/>
+      </c>
+      <c r="L18" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_fitted,3)="","",INDEX(fv_s_fitted,3)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6">
+        <f>IFERROR(INDEX(fm_dist,4)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="B19" s="26">
+        <f>IFERROR(IF(INDEX(fm_ap,4)="","",INDEX(fm_ap,4)),"")</f>
+        <v/>
+      </c>
+      <c r="C19" s="32">
+        <f>IFERROR(IF(INDEX(fm_n_above,4)="","",INDEX(fm_n_above,4)),"")</f>
+        <v/>
+      </c>
+      <c r="D19" s="26">
+        <f>IFERROR(IF(INDEX(fm_mean_excess_empirical,4)="","",INDEX(fm_mean_excess_empirical,4)),"")</f>
+        <v/>
+      </c>
+      <c r="E19" s="26">
+        <f>IFERROR(IF(INDEX(fm_mean_excess_fitted,4)="","",INDEX(fm_mean_excess_fitted,4)),"")</f>
+        <v/>
+      </c>
+      <c r="F19" s="29">
+        <f>IFERROR(IF(INDEX(fm_ratio,4)="","",INDEX(fm_ratio,4)),"")</f>
+        <v/>
+      </c>
+      <c r="H19" s="6">
+        <f>IFERROR(INDEX(fv_dist,4)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="I19" s="26">
+        <f>IFERROR(IF(INDEX(fv_t,4)="","",INDEX(fv_t,4)),"")</f>
+        <v/>
+      </c>
+      <c r="J19" s="6">
+        <f>IFERROR(INDEX(fv_t_label,4)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="K19" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_km,4)="","",INDEX(fv_s_km,4)),"")</f>
+        <v/>
+      </c>
+      <c r="L19" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_fitted,4)="","",INDEX(fv_s_fitted,4)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6">
+        <f>IFERROR(INDEX(fm_dist,5)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="B20" s="26">
+        <f>IFERROR(IF(INDEX(fm_ap,5)="","",INDEX(fm_ap,5)),"")</f>
+        <v/>
+      </c>
+      <c r="C20" s="32">
+        <f>IFERROR(IF(INDEX(fm_n_above,5)="","",INDEX(fm_n_above,5)),"")</f>
+        <v/>
+      </c>
+      <c r="D20" s="26">
+        <f>IFERROR(IF(INDEX(fm_mean_excess_empirical,5)="","",INDEX(fm_mean_excess_empirical,5)),"")</f>
+        <v/>
+      </c>
+      <c r="E20" s="26">
+        <f>IFERROR(IF(INDEX(fm_mean_excess_fitted,5)="","",INDEX(fm_mean_excess_fitted,5)),"")</f>
+        <v/>
+      </c>
+      <c r="F20" s="29">
+        <f>IFERROR(IF(INDEX(fm_ratio,5)="","",INDEX(fm_ratio,5)),"")</f>
+        <v/>
+      </c>
+      <c r="H20" s="6">
+        <f>IFERROR(INDEX(fv_dist,5)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="I20" s="26">
+        <f>IFERROR(IF(INDEX(fv_t,5)="","",INDEX(fv_t,5)),"")</f>
+        <v/>
+      </c>
+      <c r="J20" s="6">
+        <f>IFERROR(INDEX(fv_t_label,5)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="K20" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_km,5)="","",INDEX(fv_s_km,5)),"")</f>
+        <v/>
+      </c>
+      <c r="L20" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_fitted,5)="","",INDEX(fv_s_fitted,5)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6">
+        <f>IFERROR(INDEX(fm_dist,6)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="B21" s="26">
+        <f>IFERROR(IF(INDEX(fm_ap,6)="","",INDEX(fm_ap,6)),"")</f>
+        <v/>
+      </c>
+      <c r="C21" s="32">
+        <f>IFERROR(IF(INDEX(fm_n_above,6)="","",INDEX(fm_n_above,6)),"")</f>
+        <v/>
+      </c>
+      <c r="D21" s="26">
+        <f>IFERROR(IF(INDEX(fm_mean_excess_empirical,6)="","",INDEX(fm_mean_excess_empirical,6)),"")</f>
+        <v/>
+      </c>
+      <c r="E21" s="26">
+        <f>IFERROR(IF(INDEX(fm_mean_excess_fitted,6)="","",INDEX(fm_mean_excess_fitted,6)),"")</f>
+        <v/>
+      </c>
+      <c r="F21" s="29">
+        <f>IFERROR(IF(INDEX(fm_ratio,6)="","",INDEX(fm_ratio,6)),"")</f>
+        <v/>
+      </c>
+      <c r="H21" s="6">
+        <f>IFERROR(INDEX(fv_dist,6)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="I21" s="26">
+        <f>IFERROR(IF(INDEX(fv_t,6)="","",INDEX(fv_t,6)),"")</f>
+        <v/>
+      </c>
+      <c r="J21" s="6">
+        <f>IFERROR(INDEX(fv_t_label,6)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="K21" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_km,6)="","",INDEX(fv_s_km,6)),"")</f>
+        <v/>
+      </c>
+      <c r="L21" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_fitted,6)="","",INDEX(fv_s_fitted,6)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6">
+        <f>IFERROR(INDEX(fm_dist,7)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="B22" s="26">
+        <f>IFERROR(IF(INDEX(fm_ap,7)="","",INDEX(fm_ap,7)),"")</f>
+        <v/>
+      </c>
+      <c r="C22" s="32">
+        <f>IFERROR(IF(INDEX(fm_n_above,7)="","",INDEX(fm_n_above,7)),"")</f>
+        <v/>
+      </c>
+      <c r="D22" s="26">
+        <f>IFERROR(IF(INDEX(fm_mean_excess_empirical,7)="","",INDEX(fm_mean_excess_empirical,7)),"")</f>
+        <v/>
+      </c>
+      <c r="E22" s="26">
+        <f>IFERROR(IF(INDEX(fm_mean_excess_fitted,7)="","",INDEX(fm_mean_excess_fitted,7)),"")</f>
+        <v/>
+      </c>
+      <c r="F22" s="29">
+        <f>IFERROR(IF(INDEX(fm_ratio,7)="","",INDEX(fm_ratio,7)),"")</f>
+        <v/>
+      </c>
+      <c r="H22" s="6">
+        <f>IFERROR(INDEX(fv_dist,7)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="I22" s="26">
+        <f>IFERROR(IF(INDEX(fv_t,7)="","",INDEX(fv_t,7)),"")</f>
+        <v/>
+      </c>
+      <c r="J22" s="6">
+        <f>IFERROR(INDEX(fv_t_label,7)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="K22" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_km,7)="","",INDEX(fv_s_km,7)),"")</f>
+        <v/>
+      </c>
+      <c r="L22" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_fitted,7)="","",INDEX(fv_s_fitted,7)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6">
+        <f>IFERROR(INDEX(fm_dist,8)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="B23" s="26">
+        <f>IFERROR(IF(INDEX(fm_ap,8)="","",INDEX(fm_ap,8)),"")</f>
+        <v/>
+      </c>
+      <c r="C23" s="32">
+        <f>IFERROR(IF(INDEX(fm_n_above,8)="","",INDEX(fm_n_above,8)),"")</f>
+        <v/>
+      </c>
+      <c r="D23" s="26">
+        <f>IFERROR(IF(INDEX(fm_mean_excess_empirical,8)="","",INDEX(fm_mean_excess_empirical,8)),"")</f>
+        <v/>
+      </c>
+      <c r="E23" s="26">
+        <f>IFERROR(IF(INDEX(fm_mean_excess_fitted,8)="","",INDEX(fm_mean_excess_fitted,8)),"")</f>
+        <v/>
+      </c>
+      <c r="F23" s="29">
+        <f>IFERROR(IF(INDEX(fm_ratio,8)="","",INDEX(fm_ratio,8)),"")</f>
+        <v/>
+      </c>
+      <c r="H23" s="6">
+        <f>IFERROR(INDEX(fv_dist,8)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="I23" s="26">
+        <f>IFERROR(IF(INDEX(fv_t,8)="","",INDEX(fv_t,8)),"")</f>
+        <v/>
+      </c>
+      <c r="J23" s="6">
+        <f>IFERROR(INDEX(fv_t_label,8)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="K23" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_km,8)="","",INDEX(fv_s_km,8)),"")</f>
+        <v/>
+      </c>
+      <c r="L23" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_fitted,8)="","",INDEX(fv_s_fitted,8)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6">
+        <f>IFERROR(INDEX(fm_dist,9)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="B24" s="26">
+        <f>IFERROR(IF(INDEX(fm_ap,9)="","",INDEX(fm_ap,9)),"")</f>
+        <v/>
+      </c>
+      <c r="C24" s="32">
+        <f>IFERROR(IF(INDEX(fm_n_above,9)="","",INDEX(fm_n_above,9)),"")</f>
+        <v/>
+      </c>
+      <c r="D24" s="26">
+        <f>IFERROR(IF(INDEX(fm_mean_excess_empirical,9)="","",INDEX(fm_mean_excess_empirical,9)),"")</f>
+        <v/>
+      </c>
+      <c r="E24" s="26">
+        <f>IFERROR(IF(INDEX(fm_mean_excess_fitted,9)="","",INDEX(fm_mean_excess_fitted,9)),"")</f>
+        <v/>
+      </c>
+      <c r="F24" s="29">
+        <f>IFERROR(IF(INDEX(fm_ratio,9)="","",INDEX(fm_ratio,9)),"")</f>
+        <v/>
+      </c>
+      <c r="H24" s="6">
+        <f>IFERROR(INDEX(fv_dist,9)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="I24" s="26">
+        <f>IFERROR(IF(INDEX(fv_t,9)="","",INDEX(fv_t,9)),"")</f>
+        <v/>
+      </c>
+      <c r="J24" s="6">
+        <f>IFERROR(INDEX(fv_t_label,9)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="K24" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_km,9)="","",INDEX(fv_s_km,9)),"")</f>
+        <v/>
+      </c>
+      <c r="L24" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_fitted,9)="","",INDEX(fv_s_fitted,9)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6">
+        <f>IFERROR(INDEX(fm_dist,10)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="B25" s="26">
+        <f>IFERROR(IF(INDEX(fm_ap,10)="","",INDEX(fm_ap,10)),"")</f>
+        <v/>
+      </c>
+      <c r="C25" s="32">
+        <f>IFERROR(IF(INDEX(fm_n_above,10)="","",INDEX(fm_n_above,10)),"")</f>
+        <v/>
+      </c>
+      <c r="D25" s="26">
+        <f>IFERROR(IF(INDEX(fm_mean_excess_empirical,10)="","",INDEX(fm_mean_excess_empirical,10)),"")</f>
+        <v/>
+      </c>
+      <c r="E25" s="26">
+        <f>IFERROR(IF(INDEX(fm_mean_excess_fitted,10)="","",INDEX(fm_mean_excess_fitted,10)),"")</f>
+        <v/>
+      </c>
+      <c r="F25" s="29">
+        <f>IFERROR(IF(INDEX(fm_ratio,10)="","",INDEX(fm_ratio,10)),"")</f>
+        <v/>
+      </c>
+      <c r="H25" s="6">
+        <f>IFERROR(INDEX(fv_dist,10)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="I25" s="26">
+        <f>IFERROR(IF(INDEX(fv_t,10)="","",INDEX(fv_t,10)),"")</f>
+        <v/>
+      </c>
+      <c r="J25" s="6">
+        <f>IFERROR(INDEX(fv_t_label,10)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="K25" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_km,10)="","",INDEX(fv_s_km,10)),"")</f>
+        <v/>
+      </c>
+      <c r="L25" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_fitted,10)="","",INDEX(fv_s_fitted,10)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6">
+        <f>IFERROR(INDEX(fm_dist,11)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="B26" s="26">
+        <f>IFERROR(IF(INDEX(fm_ap,11)="","",INDEX(fm_ap,11)),"")</f>
+        <v/>
+      </c>
+      <c r="C26" s="32">
+        <f>IFERROR(IF(INDEX(fm_n_above,11)="","",INDEX(fm_n_above,11)),"")</f>
+        <v/>
+      </c>
+      <c r="D26" s="26">
+        <f>IFERROR(IF(INDEX(fm_mean_excess_empirical,11)="","",INDEX(fm_mean_excess_empirical,11)),"")</f>
+        <v/>
+      </c>
+      <c r="E26" s="26">
+        <f>IFERROR(IF(INDEX(fm_mean_excess_fitted,11)="","",INDEX(fm_mean_excess_fitted,11)),"")</f>
+        <v/>
+      </c>
+      <c r="F26" s="29">
+        <f>IFERROR(IF(INDEX(fm_ratio,11)="","",INDEX(fm_ratio,11)),"")</f>
+        <v/>
+      </c>
+      <c r="H26" s="6">
+        <f>IFERROR(INDEX(fv_dist,11)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="I26" s="26">
+        <f>IFERROR(IF(INDEX(fv_t,11)="","",INDEX(fv_t,11)),"")</f>
+        <v/>
+      </c>
+      <c r="J26" s="6">
+        <f>IFERROR(INDEX(fv_t_label,11)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="K26" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_km,11)="","",INDEX(fv_s_km,11)),"")</f>
+        <v/>
+      </c>
+      <c r="L26" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_fitted,11)="","",INDEX(fv_s_fitted,11)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6">
+        <f>IFERROR(INDEX(fm_dist,12)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="B27" s="26">
+        <f>IFERROR(IF(INDEX(fm_ap,12)="","",INDEX(fm_ap,12)),"")</f>
+        <v/>
+      </c>
+      <c r="C27" s="32">
+        <f>IFERROR(IF(INDEX(fm_n_above,12)="","",INDEX(fm_n_above,12)),"")</f>
+        <v/>
+      </c>
+      <c r="D27" s="26">
+        <f>IFERROR(IF(INDEX(fm_mean_excess_empirical,12)="","",INDEX(fm_mean_excess_empirical,12)),"")</f>
+        <v/>
+      </c>
+      <c r="E27" s="26">
+        <f>IFERROR(IF(INDEX(fm_mean_excess_fitted,12)="","",INDEX(fm_mean_excess_fitted,12)),"")</f>
+        <v/>
+      </c>
+      <c r="F27" s="29">
+        <f>IFERROR(IF(INDEX(fm_ratio,12)="","",INDEX(fm_ratio,12)),"")</f>
+        <v/>
+      </c>
+      <c r="H27" s="6">
+        <f>IFERROR(INDEX(fv_dist,12)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="I27" s="26">
+        <f>IFERROR(IF(INDEX(fv_t,12)="","",INDEX(fv_t,12)),"")</f>
+        <v/>
+      </c>
+      <c r="J27" s="6">
+        <f>IFERROR(INDEX(fv_t_label,12)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="K27" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_km,12)="","",INDEX(fv_s_km,12)),"")</f>
+        <v/>
+      </c>
+      <c r="L27" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_fitted,12)="","",INDEX(fv_s_fitted,12)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6">
+        <f>IFERROR(INDEX(fm_dist,13)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="B28" s="26">
+        <f>IFERROR(IF(INDEX(fm_ap,13)="","",INDEX(fm_ap,13)),"")</f>
+        <v/>
+      </c>
+      <c r="C28" s="32">
+        <f>IFERROR(IF(INDEX(fm_n_above,13)="","",INDEX(fm_n_above,13)),"")</f>
+        <v/>
+      </c>
+      <c r="D28" s="26">
+        <f>IFERROR(IF(INDEX(fm_mean_excess_empirical,13)="","",INDEX(fm_mean_excess_empirical,13)),"")</f>
+        <v/>
+      </c>
+      <c r="E28" s="26">
+        <f>IFERROR(IF(INDEX(fm_mean_excess_fitted,13)="","",INDEX(fm_mean_excess_fitted,13)),"")</f>
+        <v/>
+      </c>
+      <c r="F28" s="29">
+        <f>IFERROR(IF(INDEX(fm_ratio,13)="","",INDEX(fm_ratio,13)),"")</f>
+        <v/>
+      </c>
+      <c r="H28" s="6">
+        <f>IFERROR(INDEX(fv_dist,13)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="I28" s="26">
+        <f>IFERROR(IF(INDEX(fv_t,13)="","",INDEX(fv_t,13)),"")</f>
+        <v/>
+      </c>
+      <c r="J28" s="6">
+        <f>IFERROR(INDEX(fv_t_label,13)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="K28" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_km,13)="","",INDEX(fv_s_km,13)),"")</f>
+        <v/>
+      </c>
+      <c r="L28" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_fitted,13)="","",INDEX(fv_s_fitted,13)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6">
+        <f>IFERROR(INDEX(fm_dist,14)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="B29" s="26">
+        <f>IFERROR(IF(INDEX(fm_ap,14)="","",INDEX(fm_ap,14)),"")</f>
+        <v/>
+      </c>
+      <c r="C29" s="32">
+        <f>IFERROR(IF(INDEX(fm_n_above,14)="","",INDEX(fm_n_above,14)),"")</f>
+        <v/>
+      </c>
+      <c r="D29" s="26">
+        <f>IFERROR(IF(INDEX(fm_mean_excess_empirical,14)="","",INDEX(fm_mean_excess_empirical,14)),"")</f>
+        <v/>
+      </c>
+      <c r="E29" s="26">
+        <f>IFERROR(IF(INDEX(fm_mean_excess_fitted,14)="","",INDEX(fm_mean_excess_fitted,14)),"")</f>
+        <v/>
+      </c>
+      <c r="F29" s="29">
+        <f>IFERROR(IF(INDEX(fm_ratio,14)="","",INDEX(fm_ratio,14)),"")</f>
+        <v/>
+      </c>
+      <c r="H29" s="6">
+        <f>IFERROR(INDEX(fv_dist,14)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="I29" s="26">
+        <f>IFERROR(IF(INDEX(fv_t,14)="","",INDEX(fv_t,14)),"")</f>
+        <v/>
+      </c>
+      <c r="J29" s="6">
+        <f>IFERROR(INDEX(fv_t_label,14)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="K29" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_km,14)="","",INDEX(fv_s_km,14)),"")</f>
+        <v/>
+      </c>
+      <c r="L29" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_fitted,14)="","",INDEX(fv_s_fitted,14)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6">
+        <f>IFERROR(INDEX(fm_dist,15)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="B30" s="26">
+        <f>IFERROR(IF(INDEX(fm_ap,15)="","",INDEX(fm_ap,15)),"")</f>
+        <v/>
+      </c>
+      <c r="C30" s="32">
+        <f>IFERROR(IF(INDEX(fm_n_above,15)="","",INDEX(fm_n_above,15)),"")</f>
+        <v/>
+      </c>
+      <c r="D30" s="26">
+        <f>IFERROR(IF(INDEX(fm_mean_excess_empirical,15)="","",INDEX(fm_mean_excess_empirical,15)),"")</f>
+        <v/>
+      </c>
+      <c r="E30" s="26">
+        <f>IFERROR(IF(INDEX(fm_mean_excess_fitted,15)="","",INDEX(fm_mean_excess_fitted,15)),"")</f>
+        <v/>
+      </c>
+      <c r="F30" s="29">
+        <f>IFERROR(IF(INDEX(fm_ratio,15)="","",INDEX(fm_ratio,15)),"")</f>
+        <v/>
+      </c>
+      <c r="H30" s="6">
+        <f>IFERROR(INDEX(fv_dist,15)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="I30" s="26">
+        <f>IFERROR(IF(INDEX(fv_t,15)="","",INDEX(fv_t,15)),"")</f>
+        <v/>
+      </c>
+      <c r="J30" s="6">
+        <f>IFERROR(INDEX(fv_t_label,15)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="K30" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_km,15)="","",INDEX(fv_s_km,15)),"")</f>
+        <v/>
+      </c>
+      <c r="L30" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_fitted,15)="","",INDEX(fv_s_fitted,15)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6">
+        <f>IFERROR(INDEX(fm_dist,16)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="B31" s="26">
+        <f>IFERROR(IF(INDEX(fm_ap,16)="","",INDEX(fm_ap,16)),"")</f>
+        <v/>
+      </c>
+      <c r="C31" s="32">
+        <f>IFERROR(IF(INDEX(fm_n_above,16)="","",INDEX(fm_n_above,16)),"")</f>
+        <v/>
+      </c>
+      <c r="D31" s="26">
+        <f>IFERROR(IF(INDEX(fm_mean_excess_empirical,16)="","",INDEX(fm_mean_excess_empirical,16)),"")</f>
+        <v/>
+      </c>
+      <c r="E31" s="26">
+        <f>IFERROR(IF(INDEX(fm_mean_excess_fitted,16)="","",INDEX(fm_mean_excess_fitted,16)),"")</f>
+        <v/>
+      </c>
+      <c r="F31" s="29">
+        <f>IFERROR(IF(INDEX(fm_ratio,16)="","",INDEX(fm_ratio,16)),"")</f>
+        <v/>
+      </c>
+      <c r="H31" s="6">
+        <f>IFERROR(INDEX(fv_dist,16)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="I31" s="26">
+        <f>IFERROR(IF(INDEX(fv_t,16)="","",INDEX(fv_t,16)),"")</f>
+        <v/>
+      </c>
+      <c r="J31" s="6">
+        <f>IFERROR(INDEX(fv_t_label,16)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="K31" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_km,16)="","",INDEX(fv_s_km,16)),"")</f>
+        <v/>
+      </c>
+      <c r="L31" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_fitted,16)="","",INDEX(fv_s_fitted,16)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6">
+        <f>IFERROR(INDEX(fm_dist,17)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="B32" s="26">
+        <f>IFERROR(IF(INDEX(fm_ap,17)="","",INDEX(fm_ap,17)),"")</f>
+        <v/>
+      </c>
+      <c r="C32" s="32">
+        <f>IFERROR(IF(INDEX(fm_n_above,17)="","",INDEX(fm_n_above,17)),"")</f>
+        <v/>
+      </c>
+      <c r="D32" s="26">
+        <f>IFERROR(IF(INDEX(fm_mean_excess_empirical,17)="","",INDEX(fm_mean_excess_empirical,17)),"")</f>
+        <v/>
+      </c>
+      <c r="E32" s="26">
+        <f>IFERROR(IF(INDEX(fm_mean_excess_fitted,17)="","",INDEX(fm_mean_excess_fitted,17)),"")</f>
+        <v/>
+      </c>
+      <c r="F32" s="29">
+        <f>IFERROR(IF(INDEX(fm_ratio,17)="","",INDEX(fm_ratio,17)),"")</f>
+        <v/>
+      </c>
+      <c r="H32" s="6">
+        <f>IFERROR(INDEX(fv_dist,17)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="I32" s="26">
+        <f>IFERROR(IF(INDEX(fv_t,17)="","",INDEX(fv_t,17)),"")</f>
+        <v/>
+      </c>
+      <c r="J32" s="6">
+        <f>IFERROR(INDEX(fv_t_label,17)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="K32" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_km,17)="","",INDEX(fv_s_km,17)),"")</f>
+        <v/>
+      </c>
+      <c r="L32" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_fitted,17)="","",INDEX(fv_s_fitted,17)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6">
+        <f>IFERROR(INDEX(fm_dist,18)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="B33" s="26">
+        <f>IFERROR(IF(INDEX(fm_ap,18)="","",INDEX(fm_ap,18)),"")</f>
+        <v/>
+      </c>
+      <c r="C33" s="32">
+        <f>IFERROR(IF(INDEX(fm_n_above,18)="","",INDEX(fm_n_above,18)),"")</f>
+        <v/>
+      </c>
+      <c r="D33" s="26">
+        <f>IFERROR(IF(INDEX(fm_mean_excess_empirical,18)="","",INDEX(fm_mean_excess_empirical,18)),"")</f>
+        <v/>
+      </c>
+      <c r="E33" s="26">
+        <f>IFERROR(IF(INDEX(fm_mean_excess_fitted,18)="","",INDEX(fm_mean_excess_fitted,18)),"")</f>
+        <v/>
+      </c>
+      <c r="F33" s="29">
+        <f>IFERROR(IF(INDEX(fm_ratio,18)="","",INDEX(fm_ratio,18)),"")</f>
+        <v/>
+      </c>
+      <c r="H33" s="6">
+        <f>IFERROR(INDEX(fv_dist,18)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="I33" s="26">
+        <f>IFERROR(IF(INDEX(fv_t,18)="","",INDEX(fv_t,18)),"")</f>
+        <v/>
+      </c>
+      <c r="J33" s="6">
+        <f>IFERROR(INDEX(fv_t_label,18)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="K33" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_km,18)="","",INDEX(fv_s_km,18)),"")</f>
+        <v/>
+      </c>
+      <c r="L33" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_fitted,18)="","",INDEX(fv_s_fitted,18)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6">
+        <f>IFERROR(INDEX(fm_dist,19)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="B34" s="26">
+        <f>IFERROR(IF(INDEX(fm_ap,19)="","",INDEX(fm_ap,19)),"")</f>
+        <v/>
+      </c>
+      <c r="C34" s="32">
+        <f>IFERROR(IF(INDEX(fm_n_above,19)="","",INDEX(fm_n_above,19)),"")</f>
+        <v/>
+      </c>
+      <c r="D34" s="26">
+        <f>IFERROR(IF(INDEX(fm_mean_excess_empirical,19)="","",INDEX(fm_mean_excess_empirical,19)),"")</f>
+        <v/>
+      </c>
+      <c r="E34" s="26">
+        <f>IFERROR(IF(INDEX(fm_mean_excess_fitted,19)="","",INDEX(fm_mean_excess_fitted,19)),"")</f>
+        <v/>
+      </c>
+      <c r="F34" s="29">
+        <f>IFERROR(IF(INDEX(fm_ratio,19)="","",INDEX(fm_ratio,19)),"")</f>
+        <v/>
+      </c>
+      <c r="H34" s="6">
+        <f>IFERROR(INDEX(fv_dist,19)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="I34" s="26">
+        <f>IFERROR(IF(INDEX(fv_t,19)="","",INDEX(fv_t,19)),"")</f>
+        <v/>
+      </c>
+      <c r="J34" s="6">
+        <f>IFERROR(INDEX(fv_t_label,19)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="K34" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_km,19)="","",INDEX(fv_s_km,19)),"")</f>
+        <v/>
+      </c>
+      <c r="L34" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_fitted,19)="","",INDEX(fv_s_fitted,19)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6">
+        <f>IFERROR(INDEX(fm_dist,20)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="B35" s="26">
+        <f>IFERROR(IF(INDEX(fm_ap,20)="","",INDEX(fm_ap,20)),"")</f>
+        <v/>
+      </c>
+      <c r="C35" s="32">
+        <f>IFERROR(IF(INDEX(fm_n_above,20)="","",INDEX(fm_n_above,20)),"")</f>
+        <v/>
+      </c>
+      <c r="D35" s="26">
+        <f>IFERROR(IF(INDEX(fm_mean_excess_empirical,20)="","",INDEX(fm_mean_excess_empirical,20)),"")</f>
+        <v/>
+      </c>
+      <c r="E35" s="26">
+        <f>IFERROR(IF(INDEX(fm_mean_excess_fitted,20)="","",INDEX(fm_mean_excess_fitted,20)),"")</f>
+        <v/>
+      </c>
+      <c r="F35" s="29">
+        <f>IFERROR(IF(INDEX(fm_ratio,20)="","",INDEX(fm_ratio,20)),"")</f>
+        <v/>
+      </c>
+      <c r="H35" s="6">
+        <f>IFERROR(INDEX(fv_dist,20)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="I35" s="26">
+        <f>IFERROR(IF(INDEX(fv_t,20)="","",INDEX(fv_t,20)),"")</f>
+        <v/>
+      </c>
+      <c r="J35" s="6">
+        <f>IFERROR(INDEX(fv_t_label,20)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="K35" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_km,20)="","",INDEX(fv_s_km,20)),"")</f>
+        <v/>
+      </c>
+      <c r="L35" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_fitted,20)="","",INDEX(fv_s_fitted,20)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6">
+        <f>IFERROR(INDEX(fm_dist,21)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="B36" s="26">
+        <f>IFERROR(IF(INDEX(fm_ap,21)="","",INDEX(fm_ap,21)),"")</f>
+        <v/>
+      </c>
+      <c r="C36" s="32">
+        <f>IFERROR(IF(INDEX(fm_n_above,21)="","",INDEX(fm_n_above,21)),"")</f>
+        <v/>
+      </c>
+      <c r="D36" s="26">
+        <f>IFERROR(IF(INDEX(fm_mean_excess_empirical,21)="","",INDEX(fm_mean_excess_empirical,21)),"")</f>
+        <v/>
+      </c>
+      <c r="E36" s="26">
+        <f>IFERROR(IF(INDEX(fm_mean_excess_fitted,21)="","",INDEX(fm_mean_excess_fitted,21)),"")</f>
+        <v/>
+      </c>
+      <c r="F36" s="29">
+        <f>IFERROR(IF(INDEX(fm_ratio,21)="","",INDEX(fm_ratio,21)),"")</f>
+        <v/>
+      </c>
+      <c r="H36" s="6">
+        <f>IFERROR(INDEX(fv_dist,21)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="I36" s="26">
+        <f>IFERROR(IF(INDEX(fv_t,21)="","",INDEX(fv_t,21)),"")</f>
+        <v/>
+      </c>
+      <c r="J36" s="6">
+        <f>IFERROR(INDEX(fv_t_label,21)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="K36" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_km,21)="","",INDEX(fv_s_km,21)),"")</f>
+        <v/>
+      </c>
+      <c r="L36" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_fitted,21)="","",INDEX(fv_s_fitted,21)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6">
+        <f>IFERROR(INDEX(fm_dist,22)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="B37" s="26">
+        <f>IFERROR(IF(INDEX(fm_ap,22)="","",INDEX(fm_ap,22)),"")</f>
+        <v/>
+      </c>
+      <c r="C37" s="32">
+        <f>IFERROR(IF(INDEX(fm_n_above,22)="","",INDEX(fm_n_above,22)),"")</f>
+        <v/>
+      </c>
+      <c r="D37" s="26">
+        <f>IFERROR(IF(INDEX(fm_mean_excess_empirical,22)="","",INDEX(fm_mean_excess_empirical,22)),"")</f>
+        <v/>
+      </c>
+      <c r="E37" s="26">
+        <f>IFERROR(IF(INDEX(fm_mean_excess_fitted,22)="","",INDEX(fm_mean_excess_fitted,22)),"")</f>
+        <v/>
+      </c>
+      <c r="F37" s="29">
+        <f>IFERROR(IF(INDEX(fm_ratio,22)="","",INDEX(fm_ratio,22)),"")</f>
+        <v/>
+      </c>
+      <c r="H37" s="6">
+        <f>IFERROR(INDEX(fv_dist,22)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="I37" s="26">
+        <f>IFERROR(IF(INDEX(fv_t,22)="","",INDEX(fv_t,22)),"")</f>
+        <v/>
+      </c>
+      <c r="J37" s="6">
+        <f>IFERROR(INDEX(fv_t_label,22)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="K37" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_km,22)="","",INDEX(fv_s_km,22)),"")</f>
+        <v/>
+      </c>
+      <c r="L37" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_fitted,22)="","",INDEX(fv_s_fitted,22)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6">
+        <f>IFERROR(INDEX(fm_dist,23)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="B38" s="26">
+        <f>IFERROR(IF(INDEX(fm_ap,23)="","",INDEX(fm_ap,23)),"")</f>
+        <v/>
+      </c>
+      <c r="C38" s="32">
+        <f>IFERROR(IF(INDEX(fm_n_above,23)="","",INDEX(fm_n_above,23)),"")</f>
+        <v/>
+      </c>
+      <c r="D38" s="26">
+        <f>IFERROR(IF(INDEX(fm_mean_excess_empirical,23)="","",INDEX(fm_mean_excess_empirical,23)),"")</f>
+        <v/>
+      </c>
+      <c r="E38" s="26">
+        <f>IFERROR(IF(INDEX(fm_mean_excess_fitted,23)="","",INDEX(fm_mean_excess_fitted,23)),"")</f>
+        <v/>
+      </c>
+      <c r="F38" s="29">
+        <f>IFERROR(IF(INDEX(fm_ratio,23)="","",INDEX(fm_ratio,23)),"")</f>
+        <v/>
+      </c>
+      <c r="H38" s="6">
+        <f>IFERROR(INDEX(fv_dist,23)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="I38" s="26">
+        <f>IFERROR(IF(INDEX(fv_t,23)="","",INDEX(fv_t,23)),"")</f>
+        <v/>
+      </c>
+      <c r="J38" s="6">
+        <f>IFERROR(INDEX(fv_t_label,23)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="K38" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_km,23)="","",INDEX(fv_s_km,23)),"")</f>
+        <v/>
+      </c>
+      <c r="L38" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_fitted,23)="","",INDEX(fv_s_fitted,23)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6">
+        <f>IFERROR(INDEX(fm_dist,24)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="B39" s="26">
+        <f>IFERROR(IF(INDEX(fm_ap,24)="","",INDEX(fm_ap,24)),"")</f>
+        <v/>
+      </c>
+      <c r="C39" s="32">
+        <f>IFERROR(IF(INDEX(fm_n_above,24)="","",INDEX(fm_n_above,24)),"")</f>
+        <v/>
+      </c>
+      <c r="D39" s="26">
+        <f>IFERROR(IF(INDEX(fm_mean_excess_empirical,24)="","",INDEX(fm_mean_excess_empirical,24)),"")</f>
+        <v/>
+      </c>
+      <c r="E39" s="26">
+        <f>IFERROR(IF(INDEX(fm_mean_excess_fitted,24)="","",INDEX(fm_mean_excess_fitted,24)),"")</f>
+        <v/>
+      </c>
+      <c r="F39" s="29">
+        <f>IFERROR(IF(INDEX(fm_ratio,24)="","",INDEX(fm_ratio,24)),"")</f>
+        <v/>
+      </c>
+      <c r="H39" s="6">
+        <f>IFERROR(INDEX(fv_dist,24)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="I39" s="26">
+        <f>IFERROR(IF(INDEX(fv_t,24)="","",INDEX(fv_t,24)),"")</f>
+        <v/>
+      </c>
+      <c r="J39" s="6">
+        <f>IFERROR(INDEX(fv_t_label,24)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="K39" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_km,24)="","",INDEX(fv_s_km,24)),"")</f>
+        <v/>
+      </c>
+      <c r="L39" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_fitted,24)="","",INDEX(fv_s_fitted,24)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6">
+        <f>IFERROR(INDEX(fm_dist,25)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="B40" s="26">
+        <f>IFERROR(IF(INDEX(fm_ap,25)="","",INDEX(fm_ap,25)),"")</f>
+        <v/>
+      </c>
+      <c r="C40" s="32">
+        <f>IFERROR(IF(INDEX(fm_n_above,25)="","",INDEX(fm_n_above,25)),"")</f>
+        <v/>
+      </c>
+      <c r="D40" s="26">
+        <f>IFERROR(IF(INDEX(fm_mean_excess_empirical,25)="","",INDEX(fm_mean_excess_empirical,25)),"")</f>
+        <v/>
+      </c>
+      <c r="E40" s="26">
+        <f>IFERROR(IF(INDEX(fm_mean_excess_fitted,25)="","",INDEX(fm_mean_excess_fitted,25)),"")</f>
+        <v/>
+      </c>
+      <c r="F40" s="29">
+        <f>IFERROR(IF(INDEX(fm_ratio,25)="","",INDEX(fm_ratio,25)),"")</f>
+        <v/>
+      </c>
+      <c r="H40" s="6">
+        <f>IFERROR(INDEX(fv_dist,25)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="I40" s="26">
+        <f>IFERROR(IF(INDEX(fv_t,25)="","",INDEX(fv_t,25)),"")</f>
+        <v/>
+      </c>
+      <c r="J40" s="6">
+        <f>IFERROR(INDEX(fv_t_label,25)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="K40" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_km,25)="","",INDEX(fv_s_km,25)),"")</f>
+        <v/>
+      </c>
+      <c r="L40" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_fitted,25)="","",INDEX(fv_s_fitted,25)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6">
+        <f>IFERROR(INDEX(fm_dist,26)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="B41" s="26">
+        <f>IFERROR(IF(INDEX(fm_ap,26)="","",INDEX(fm_ap,26)),"")</f>
+        <v/>
+      </c>
+      <c r="C41" s="32">
+        <f>IFERROR(IF(INDEX(fm_n_above,26)="","",INDEX(fm_n_above,26)),"")</f>
+        <v/>
+      </c>
+      <c r="D41" s="26">
+        <f>IFERROR(IF(INDEX(fm_mean_excess_empirical,26)="","",INDEX(fm_mean_excess_empirical,26)),"")</f>
+        <v/>
+      </c>
+      <c r="E41" s="26">
+        <f>IFERROR(IF(INDEX(fm_mean_excess_fitted,26)="","",INDEX(fm_mean_excess_fitted,26)),"")</f>
+        <v/>
+      </c>
+      <c r="F41" s="29">
+        <f>IFERROR(IF(INDEX(fm_ratio,26)="","",INDEX(fm_ratio,26)),"")</f>
+        <v/>
+      </c>
+      <c r="H41" s="6">
+        <f>IFERROR(INDEX(fv_dist,26)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="I41" s="26">
+        <f>IFERROR(IF(INDEX(fv_t,26)="","",INDEX(fv_t,26)),"")</f>
+        <v/>
+      </c>
+      <c r="J41" s="6">
+        <f>IFERROR(INDEX(fv_t_label,26)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="K41" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_km,26)="","",INDEX(fv_s_km,26)),"")</f>
+        <v/>
+      </c>
+      <c r="L41" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_fitted,26)="","",INDEX(fv_s_fitted,26)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6">
+        <f>IFERROR(INDEX(fm_dist,27)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="B42" s="26">
+        <f>IFERROR(IF(INDEX(fm_ap,27)="","",INDEX(fm_ap,27)),"")</f>
+        <v/>
+      </c>
+      <c r="C42" s="32">
+        <f>IFERROR(IF(INDEX(fm_n_above,27)="","",INDEX(fm_n_above,27)),"")</f>
+        <v/>
+      </c>
+      <c r="D42" s="26">
+        <f>IFERROR(IF(INDEX(fm_mean_excess_empirical,27)="","",INDEX(fm_mean_excess_empirical,27)),"")</f>
+        <v/>
+      </c>
+      <c r="E42" s="26">
+        <f>IFERROR(IF(INDEX(fm_mean_excess_fitted,27)="","",INDEX(fm_mean_excess_fitted,27)),"")</f>
+        <v/>
+      </c>
+      <c r="F42" s="29">
+        <f>IFERROR(IF(INDEX(fm_ratio,27)="","",INDEX(fm_ratio,27)),"")</f>
+        <v/>
+      </c>
+      <c r="H42" s="6">
+        <f>IFERROR(INDEX(fv_dist,27)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="I42" s="26">
+        <f>IFERROR(IF(INDEX(fv_t,27)="","",INDEX(fv_t,27)),"")</f>
+        <v/>
+      </c>
+      <c r="J42" s="6">
+        <f>IFERROR(INDEX(fv_t_label,27)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="K42" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_km,27)="","",INDEX(fv_s_km,27)),"")</f>
+        <v/>
+      </c>
+      <c r="L42" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_fitted,27)="","",INDEX(fv_s_fitted,27)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6">
+        <f>IFERROR(INDEX(fm_dist,28)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="B43" s="26">
+        <f>IFERROR(IF(INDEX(fm_ap,28)="","",INDEX(fm_ap,28)),"")</f>
+        <v/>
+      </c>
+      <c r="C43" s="32">
+        <f>IFERROR(IF(INDEX(fm_n_above,28)="","",INDEX(fm_n_above,28)),"")</f>
+        <v/>
+      </c>
+      <c r="D43" s="26">
+        <f>IFERROR(IF(INDEX(fm_mean_excess_empirical,28)="","",INDEX(fm_mean_excess_empirical,28)),"")</f>
+        <v/>
+      </c>
+      <c r="E43" s="26">
+        <f>IFERROR(IF(INDEX(fm_mean_excess_fitted,28)="","",INDEX(fm_mean_excess_fitted,28)),"")</f>
+        <v/>
+      </c>
+      <c r="F43" s="29">
+        <f>IFERROR(IF(INDEX(fm_ratio,28)="","",INDEX(fm_ratio,28)),"")</f>
+        <v/>
+      </c>
+      <c r="H43" s="6">
+        <f>IFERROR(INDEX(fv_dist,28)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="I43" s="26">
+        <f>IFERROR(IF(INDEX(fv_t,28)="","",INDEX(fv_t,28)),"")</f>
+        <v/>
+      </c>
+      <c r="J43" s="6">
+        <f>IFERROR(INDEX(fv_t_label,28)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="K43" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_km,28)="","",INDEX(fv_s_km,28)),"")</f>
+        <v/>
+      </c>
+      <c r="L43" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_fitted,28)="","",INDEX(fv_s_fitted,28)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6">
+        <f>IFERROR(INDEX(fm_dist,29)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="B44" s="26">
+        <f>IFERROR(IF(INDEX(fm_ap,29)="","",INDEX(fm_ap,29)),"")</f>
+        <v/>
+      </c>
+      <c r="C44" s="32">
+        <f>IFERROR(IF(INDEX(fm_n_above,29)="","",INDEX(fm_n_above,29)),"")</f>
+        <v/>
+      </c>
+      <c r="D44" s="26">
+        <f>IFERROR(IF(INDEX(fm_mean_excess_empirical,29)="","",INDEX(fm_mean_excess_empirical,29)),"")</f>
+        <v/>
+      </c>
+      <c r="E44" s="26">
+        <f>IFERROR(IF(INDEX(fm_mean_excess_fitted,29)="","",INDEX(fm_mean_excess_fitted,29)),"")</f>
+        <v/>
+      </c>
+      <c r="F44" s="29">
+        <f>IFERROR(IF(INDEX(fm_ratio,29)="","",INDEX(fm_ratio,29)),"")</f>
+        <v/>
+      </c>
+      <c r="H44" s="6">
+        <f>IFERROR(INDEX(fv_dist,29)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="I44" s="26">
+        <f>IFERROR(IF(INDEX(fv_t,29)="","",INDEX(fv_t,29)),"")</f>
+        <v/>
+      </c>
+      <c r="J44" s="6">
+        <f>IFERROR(INDEX(fv_t_label,29)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="K44" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_km,29)="","",INDEX(fv_s_km,29)),"")</f>
+        <v/>
+      </c>
+      <c r="L44" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_fitted,29)="","",INDEX(fv_s_fitted,29)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6">
+        <f>IFERROR(INDEX(fm_dist,30)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="B45" s="26">
+        <f>IFERROR(IF(INDEX(fm_ap,30)="","",INDEX(fm_ap,30)),"")</f>
+        <v/>
+      </c>
+      <c r="C45" s="32">
+        <f>IFERROR(IF(INDEX(fm_n_above,30)="","",INDEX(fm_n_above,30)),"")</f>
+        <v/>
+      </c>
+      <c r="D45" s="26">
+        <f>IFERROR(IF(INDEX(fm_mean_excess_empirical,30)="","",INDEX(fm_mean_excess_empirical,30)),"")</f>
+        <v/>
+      </c>
+      <c r="E45" s="26">
+        <f>IFERROR(IF(INDEX(fm_mean_excess_fitted,30)="","",INDEX(fm_mean_excess_fitted,30)),"")</f>
+        <v/>
+      </c>
+      <c r="F45" s="29">
+        <f>IFERROR(IF(INDEX(fm_ratio,30)="","",INDEX(fm_ratio,30)),"")</f>
+        <v/>
+      </c>
+      <c r="H45" s="6">
+        <f>IFERROR(INDEX(fv_dist,30)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="I45" s="26">
+        <f>IFERROR(IF(INDEX(fv_t,30)="","",INDEX(fv_t,30)),"")</f>
+        <v/>
+      </c>
+      <c r="J45" s="6">
+        <f>IFERROR(INDEX(fv_t_label,30)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="K45" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_km,30)="","",INDEX(fv_s_km,30)),"")</f>
+        <v/>
+      </c>
+      <c r="L45" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_fitted,30)="","",INDEX(fv_s_fitted,30)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="H46" s="6">
+        <f>IFERROR(INDEX(fv_dist,31)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="I46" s="26">
+        <f>IFERROR(IF(INDEX(fv_t,31)="","",INDEX(fv_t,31)),"")</f>
+        <v/>
+      </c>
+      <c r="J46" s="6">
+        <f>IFERROR(INDEX(fv_t_label,31)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="K46" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_km,31)="","",INDEX(fv_s_km,31)),"")</f>
+        <v/>
+      </c>
+      <c r="L46" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_fitted,31)="","",INDEX(fv_s_fitted,31)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="H47" s="6">
+        <f>IFERROR(INDEX(fv_dist,32)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="I47" s="26">
+        <f>IFERROR(IF(INDEX(fv_t,32)="","",INDEX(fv_t,32)),"")</f>
+        <v/>
+      </c>
+      <c r="J47" s="6">
+        <f>IFERROR(INDEX(fv_t_label,32)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="K47" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_km,32)="","",INDEX(fv_s_km,32)),"")</f>
+        <v/>
+      </c>
+      <c r="L47" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_fitted,32)="","",INDEX(fv_s_fitted,32)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="H48" s="6">
+        <f>IFERROR(INDEX(fv_dist,33)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="I48" s="26">
+        <f>IFERROR(IF(INDEX(fv_t,33)="","",INDEX(fv_t,33)),"")</f>
+        <v/>
+      </c>
+      <c r="J48" s="6">
+        <f>IFERROR(INDEX(fv_t_label,33)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="K48" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_km,33)="","",INDEX(fv_s_km,33)),"")</f>
+        <v/>
+      </c>
+      <c r="L48" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_fitted,33)="","",INDEX(fv_s_fitted,33)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="H49" s="6">
+        <f>IFERROR(INDEX(fv_dist,34)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="I49" s="26">
+        <f>IFERROR(IF(INDEX(fv_t,34)="","",INDEX(fv_t,34)),"")</f>
+        <v/>
+      </c>
+      <c r="J49" s="6">
+        <f>IFERROR(INDEX(fv_t_label,34)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="K49" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_km,34)="","",INDEX(fv_s_km,34)),"")</f>
+        <v/>
+      </c>
+      <c r="L49" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_fitted,34)="","",INDEX(fv_s_fitted,34)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="H50" s="6">
+        <f>IFERROR(INDEX(fv_dist,35)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="I50" s="26">
+        <f>IFERROR(IF(INDEX(fv_t,35)="","",INDEX(fv_t,35)),"")</f>
+        <v/>
+      </c>
+      <c r="J50" s="6">
+        <f>IFERROR(INDEX(fv_t_label,35)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="K50" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_km,35)="","",INDEX(fv_s_km,35)),"")</f>
+        <v/>
+      </c>
+      <c r="L50" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_fitted,35)="","",INDEX(fv_s_fitted,35)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="H51" s="6">
+        <f>IFERROR(INDEX(fv_dist,36)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="I51" s="26">
+        <f>IFERROR(IF(INDEX(fv_t,36)="","",INDEX(fv_t,36)),"")</f>
+        <v/>
+      </c>
+      <c r="J51" s="6">
+        <f>IFERROR(INDEX(fv_t_label,36)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="K51" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_km,36)="","",INDEX(fv_s_km,36)),"")</f>
+        <v/>
+      </c>
+      <c r="L51" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_fitted,36)="","",INDEX(fv_s_fitted,36)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="H52" s="6">
+        <f>IFERROR(INDEX(fv_dist,37)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="I52" s="26">
+        <f>IFERROR(IF(INDEX(fv_t,37)="","",INDEX(fv_t,37)),"")</f>
+        <v/>
+      </c>
+      <c r="J52" s="6">
+        <f>IFERROR(INDEX(fv_t_label,37)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="K52" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_km,37)="","",INDEX(fv_s_km,37)),"")</f>
+        <v/>
+      </c>
+      <c r="L52" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_fitted,37)="","",INDEX(fv_s_fitted,37)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="H53" s="6">
+        <f>IFERROR(INDEX(fv_dist,38)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="I53" s="26">
+        <f>IFERROR(IF(INDEX(fv_t,38)="","",INDEX(fv_t,38)),"")</f>
+        <v/>
+      </c>
+      <c r="J53" s="6">
+        <f>IFERROR(INDEX(fv_t_label,38)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="K53" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_km,38)="","",INDEX(fv_s_km,38)),"")</f>
+        <v/>
+      </c>
+      <c r="L53" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_fitted,38)="","",INDEX(fv_s_fitted,38)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="H54" s="6">
+        <f>IFERROR(INDEX(fv_dist,39)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="I54" s="26">
+        <f>IFERROR(IF(INDEX(fv_t,39)="","",INDEX(fv_t,39)),"")</f>
+        <v/>
+      </c>
+      <c r="J54" s="6">
+        <f>IFERROR(INDEX(fv_t_label,39)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="K54" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_km,39)="","",INDEX(fv_s_km,39)),"")</f>
+        <v/>
+      </c>
+      <c r="L54" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_fitted,39)="","",INDEX(fv_s_fitted,39)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="H55" s="6">
+        <f>IFERROR(INDEX(fv_dist,40)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="I55" s="26">
+        <f>IFERROR(IF(INDEX(fv_t,40)="","",INDEX(fv_t,40)),"")</f>
+        <v/>
+      </c>
+      <c r="J55" s="6">
+        <f>IFERROR(INDEX(fv_t_label,40)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="K55" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_km,40)="","",INDEX(fv_s_km,40)),"")</f>
+        <v/>
+      </c>
+      <c r="L55" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_fitted,40)="","",INDEX(fv_s_fitted,40)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="H56" s="6">
+        <f>IFERROR(INDEX(fv_dist,41)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="I56" s="26">
+        <f>IFERROR(IF(INDEX(fv_t,41)="","",INDEX(fv_t,41)),"")</f>
+        <v/>
+      </c>
+      <c r="J56" s="6">
+        <f>IFERROR(INDEX(fv_t_label,41)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="K56" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_km,41)="","",INDEX(fv_s_km,41)),"")</f>
+        <v/>
+      </c>
+      <c r="L56" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_fitted,41)="","",INDEX(fv_s_fitted,41)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="H57" s="6">
+        <f>IFERROR(INDEX(fv_dist,42)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="I57" s="26">
+        <f>IFERROR(IF(INDEX(fv_t,42)="","",INDEX(fv_t,42)),"")</f>
+        <v/>
+      </c>
+      <c r="J57" s="6">
+        <f>IFERROR(INDEX(fv_t_label,42)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="K57" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_km,42)="","",INDEX(fv_s_km,42)),"")</f>
+        <v/>
+      </c>
+      <c r="L57" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_fitted,42)="","",INDEX(fv_s_fitted,42)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="H58" s="6">
+        <f>IFERROR(INDEX(fv_dist,43)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="I58" s="26">
+        <f>IFERROR(IF(INDEX(fv_t,43)="","",INDEX(fv_t,43)),"")</f>
+        <v/>
+      </c>
+      <c r="J58" s="6">
+        <f>IFERROR(INDEX(fv_t_label,43)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="K58" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_km,43)="","",INDEX(fv_s_km,43)),"")</f>
+        <v/>
+      </c>
+      <c r="L58" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_fitted,43)="","",INDEX(fv_s_fitted,43)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="H59" s="6">
+        <f>IFERROR(INDEX(fv_dist,44)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="I59" s="26">
+        <f>IFERROR(IF(INDEX(fv_t,44)="","",INDEX(fv_t,44)),"")</f>
+        <v/>
+      </c>
+      <c r="J59" s="6">
+        <f>IFERROR(INDEX(fv_t_label,44)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="K59" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_km,44)="","",INDEX(fv_s_km,44)),"")</f>
+        <v/>
+      </c>
+      <c r="L59" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_fitted,44)="","",INDEX(fv_s_fitted,44)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="H60" s="6">
+        <f>IFERROR(INDEX(fv_dist,45)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="I60" s="26">
+        <f>IFERROR(IF(INDEX(fv_t,45)="","",INDEX(fv_t,45)),"")</f>
+        <v/>
+      </c>
+      <c r="J60" s="6">
+        <f>IFERROR(INDEX(fv_t_label,45)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="K60" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_km,45)="","",INDEX(fv_s_km,45)),"")</f>
+        <v/>
+      </c>
+      <c r="L60" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_fitted,45)="","",INDEX(fv_s_fitted,45)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="H61" s="6">
+        <f>IFERROR(INDEX(fv_dist,46)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="I61" s="26">
+        <f>IFERROR(IF(INDEX(fv_t,46)="","",INDEX(fv_t,46)),"")</f>
+        <v/>
+      </c>
+      <c r="J61" s="6">
+        <f>IFERROR(INDEX(fv_t_label,46)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="K61" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_km,46)="","",INDEX(fv_s_km,46)),"")</f>
+        <v/>
+      </c>
+      <c r="L61" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_fitted,46)="","",INDEX(fv_s_fitted,46)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="H62" s="6">
+        <f>IFERROR(INDEX(fv_dist,47)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="I62" s="26">
+        <f>IFERROR(IF(INDEX(fv_t,47)="","",INDEX(fv_t,47)),"")</f>
+        <v/>
+      </c>
+      <c r="J62" s="6">
+        <f>IFERROR(INDEX(fv_t_label,47)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="K62" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_km,47)="","",INDEX(fv_s_km,47)),"")</f>
+        <v/>
+      </c>
+      <c r="L62" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_fitted,47)="","",INDEX(fv_s_fitted,47)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="H63" s="6">
+        <f>IFERROR(INDEX(fv_dist,48)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="I63" s="26">
+        <f>IFERROR(IF(INDEX(fv_t,48)="","",INDEX(fv_t,48)),"")</f>
+        <v/>
+      </c>
+      <c r="J63" s="6">
+        <f>IFERROR(INDEX(fv_t_label,48)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="K63" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_km,48)="","",INDEX(fv_s_km,48)),"")</f>
+        <v/>
+      </c>
+      <c r="L63" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_fitted,48)="","",INDEX(fv_s_fitted,48)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="H64" s="6">
+        <f>IFERROR(INDEX(fv_dist,49)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="I64" s="26">
+        <f>IFERROR(IF(INDEX(fv_t,49)="","",INDEX(fv_t,49)),"")</f>
+        <v/>
+      </c>
+      <c r="J64" s="6">
+        <f>IFERROR(INDEX(fv_t_label,49)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="K64" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_km,49)="","",INDEX(fv_s_km,49)),"")</f>
+        <v/>
+      </c>
+      <c r="L64" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_fitted,49)="","",INDEX(fv_s_fitted,49)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="H65" s="6">
+        <f>IFERROR(INDEX(fv_dist,50)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="I65" s="26">
+        <f>IFERROR(IF(INDEX(fv_t,50)="","",INDEX(fv_t,50)),"")</f>
+        <v/>
+      </c>
+      <c r="J65" s="6">
+        <f>IFERROR(INDEX(fv_t_label,50)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="K65" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_km,50)="","",INDEX(fv_s_km,50)),"")</f>
+        <v/>
+      </c>
+      <c r="L65" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_fitted,50)="","",INDEX(fv_s_fitted,50)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="H66" s="6">
+        <f>IFERROR(INDEX(fv_dist,51)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="I66" s="26">
+        <f>IFERROR(IF(INDEX(fv_t,51)="","",INDEX(fv_t,51)),"")</f>
+        <v/>
+      </c>
+      <c r="J66" s="6">
+        <f>IFERROR(INDEX(fv_t_label,51)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="K66" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_km,51)="","",INDEX(fv_s_km,51)),"")</f>
+        <v/>
+      </c>
+      <c r="L66" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_fitted,51)="","",INDEX(fv_s_fitted,51)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="H67" s="6">
+        <f>IFERROR(INDEX(fv_dist,52)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="I67" s="26">
+        <f>IFERROR(IF(INDEX(fv_t,52)="","",INDEX(fv_t,52)),"")</f>
+        <v/>
+      </c>
+      <c r="J67" s="6">
+        <f>IFERROR(INDEX(fv_t_label,52)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="K67" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_km,52)="","",INDEX(fv_s_km,52)),"")</f>
+        <v/>
+      </c>
+      <c r="L67" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_fitted,52)="","",INDEX(fv_s_fitted,52)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="H68" s="6">
+        <f>IFERROR(INDEX(fv_dist,53)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="I68" s="26">
+        <f>IFERROR(IF(INDEX(fv_t,53)="","",INDEX(fv_t,53)),"")</f>
+        <v/>
+      </c>
+      <c r="J68" s="6">
+        <f>IFERROR(INDEX(fv_t_label,53)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="K68" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_km,53)="","",INDEX(fv_s_km,53)),"")</f>
+        <v/>
+      </c>
+      <c r="L68" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_fitted,53)="","",INDEX(fv_s_fitted,53)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="H69" s="6">
+        <f>IFERROR(INDEX(fv_dist,54)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="I69" s="26">
+        <f>IFERROR(IF(INDEX(fv_t,54)="","",INDEX(fv_t,54)),"")</f>
+        <v/>
+      </c>
+      <c r="J69" s="6">
+        <f>IFERROR(INDEX(fv_t_label,54)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="K69" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_km,54)="","",INDEX(fv_s_km,54)),"")</f>
+        <v/>
+      </c>
+      <c r="L69" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_fitted,54)="","",INDEX(fv_s_fitted,54)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="H70" s="6">
+        <f>IFERROR(INDEX(fv_dist,55)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="I70" s="26">
+        <f>IFERROR(IF(INDEX(fv_t,55)="","",INDEX(fv_t,55)),"")</f>
+        <v/>
+      </c>
+      <c r="J70" s="6">
+        <f>IFERROR(INDEX(fv_t_label,55)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="K70" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_km,55)="","",INDEX(fv_s_km,55)),"")</f>
+        <v/>
+      </c>
+      <c r="L70" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_fitted,55)="","",INDEX(fv_s_fitted,55)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="H71" s="6">
+        <f>IFERROR(INDEX(fv_dist,56)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="I71" s="26">
+        <f>IFERROR(IF(INDEX(fv_t,56)="","",INDEX(fv_t,56)),"")</f>
+        <v/>
+      </c>
+      <c r="J71" s="6">
+        <f>IFERROR(INDEX(fv_t_label,56)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="K71" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_km,56)="","",INDEX(fv_s_km,56)),"")</f>
+        <v/>
+      </c>
+      <c r="L71" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_fitted,56)="","",INDEX(fv_s_fitted,56)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="H72" s="6">
+        <f>IFERROR(INDEX(fv_dist,57)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="I72" s="26">
+        <f>IFERROR(IF(INDEX(fv_t,57)="","",INDEX(fv_t,57)),"")</f>
+        <v/>
+      </c>
+      <c r="J72" s="6">
+        <f>IFERROR(INDEX(fv_t_label,57)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="K72" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_km,57)="","",INDEX(fv_s_km,57)),"")</f>
+        <v/>
+      </c>
+      <c r="L72" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_fitted,57)="","",INDEX(fv_s_fitted,57)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="H73" s="6">
+        <f>IFERROR(INDEX(fv_dist,58)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="I73" s="26">
+        <f>IFERROR(IF(INDEX(fv_t,58)="","",INDEX(fv_t,58)),"")</f>
+        <v/>
+      </c>
+      <c r="J73" s="6">
+        <f>IFERROR(INDEX(fv_t_label,58)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="K73" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_km,58)="","",INDEX(fv_s_km,58)),"")</f>
+        <v/>
+      </c>
+      <c r="L73" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_fitted,58)="","",INDEX(fv_s_fitted,58)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="H74" s="6">
+        <f>IFERROR(INDEX(fv_dist,59)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="I74" s="26">
+        <f>IFERROR(IF(INDEX(fv_t,59)="","",INDEX(fv_t,59)),"")</f>
+        <v/>
+      </c>
+      <c r="J74" s="6">
+        <f>IFERROR(INDEX(fv_t_label,59)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="K74" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_km,59)="","",INDEX(fv_s_km,59)),"")</f>
+        <v/>
+      </c>
+      <c r="L74" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_fitted,59)="","",INDEX(fv_s_fitted,59)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="H75" s="6">
+        <f>IFERROR(INDEX(fv_dist,60)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="I75" s="26">
+        <f>IFERROR(IF(INDEX(fv_t,60)="","",INDEX(fv_t,60)),"")</f>
+        <v/>
+      </c>
+      <c r="J75" s="6">
+        <f>IFERROR(INDEX(fv_t_label,60)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="K75" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_km,60)="","",INDEX(fv_s_km,60)),"")</f>
+        <v/>
+      </c>
+      <c r="L75" s="46">
+        <f>IFERROR(IF(INDEX(fv_s_fitted,60)="","",INDEX(fv_s_fitted,60)),"")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -8800,243 +11667,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00A6A6A6"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AR1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="9" t="inlineStr">
-        <is>
-          <t>cedant</t>
-        </is>
-      </c>
-      <c r="B1" s="9" t="inlineStr">
-        <is>
-          <t>country</t>
-        </is>
-      </c>
-      <c r="C1" s="9" t="inlineStr">
-        <is>
-          <t>line</t>
-        </is>
-      </c>
-      <c r="D1" s="9" t="inlineStr">
-        <is>
-          <t>quote_ccy</t>
-        </is>
-      </c>
-      <c r="E1" s="9" t="inlineStr">
-        <is>
-          <t>fx_quote_to_usd</t>
-        </is>
-      </c>
-      <c r="F1" s="9" t="inlineStr">
-        <is>
-          <t>treaty_start</t>
-        </is>
-      </c>
-      <c r="G1" s="9" t="inlineStr">
-        <is>
-          <t>quote_year</t>
-        </is>
-      </c>
-      <c r="H1" s="9" t="inlineStr">
-        <is>
-          <t>run_label</t>
-        </is>
-      </c>
-      <c r="I1" s="9" t="inlineStr">
-        <is>
-          <t>scenario_id</t>
-        </is>
-      </c>
-      <c r="J1" s="9" t="inlineStr">
-        <is>
-          <t>source_mode</t>
-        </is>
-      </c>
-      <c r="K1" s="9" t="inlineStr">
-        <is>
-          <t>premium_basis</t>
-        </is>
-      </c>
-      <c r="L1" s="9" t="inlineStr">
-        <is>
-          <t>segment_field</t>
-        </is>
-      </c>
-      <c r="M1" s="9" t="inlineStr">
-        <is>
-          <t>ete_tpa_filter</t>
-        </is>
-      </c>
-      <c r="N1" s="9" t="inlineStr">
-        <is>
-          <t>treaty_basis</t>
-        </is>
-      </c>
-      <c r="O1" s="9" t="inlineStr">
-        <is>
-          <t>claims_trigger</t>
-        </is>
-      </c>
-      <c r="P1" s="9" t="inlineStr">
-        <is>
-          <t>paid_runoff_months</t>
-        </is>
-      </c>
-      <c r="Q1" s="9" t="inlineStr">
-        <is>
-          <t>pp_accumulation</t>
-        </is>
-      </c>
-      <c r="R1" s="9" t="inlineStr">
-        <is>
-          <t>epi_quote_year</t>
-        </is>
-      </c>
-      <c r="S1" s="9" t="inlineStr">
-        <is>
-          <t>expected_lives_quote_year</t>
-        </is>
-      </c>
-      <c r="T1" s="9" t="inlineStr">
-        <is>
-          <t>years_included</t>
-        </is>
-      </c>
-      <c r="U1" s="9" t="inlineStr">
-        <is>
-          <t>output_threshold_pct_min_ap</t>
-        </is>
-      </c>
-      <c r="V1" s="9" t="inlineStr">
-        <is>
-          <t>policy_limit</t>
-        </is>
-      </c>
-      <c r="W1" s="9" t="inlineStr">
-        <is>
-          <t>outlier_method</t>
-        </is>
-      </c>
-      <c r="X1" s="9" t="inlineStr">
-        <is>
-          <t>outlier_value</t>
-        </is>
-      </c>
-      <c r="Y1" s="9" t="inlineStr">
-        <is>
-          <t>iqr_multiplier</t>
-        </is>
-      </c>
-      <c r="Z1" s="9" t="inlineStr">
-        <is>
-          <t>full_cred_n</t>
-        </is>
-      </c>
-      <c r="AA1" s="9" t="inlineStr">
-        <is>
-          <t>complement_source</t>
-        </is>
-      </c>
-      <c r="AB1" s="9" t="inlineStr">
-        <is>
-          <t>benchmark_rate</t>
-        </is>
-      </c>
-      <c r="AC1" s="9" t="inlineStr">
-        <is>
-          <t>incidence_adj</t>
-        </is>
-      </c>
-      <c r="AD1" s="9" t="inlineStr">
-        <is>
-          <t>qs_cedant_retention_pct</t>
-        </is>
-      </c>
-      <c r="AE1" s="9" t="inlineStr">
-        <is>
-          <t>evaluate_mode</t>
-        </is>
-      </c>
-      <c r="AF1" s="9" t="inlineStr">
-        <is>
-          <t>iterations</t>
-        </is>
-      </c>
-      <c r="AG1" s="9" t="inlineStr">
-        <is>
-          <t>seed</t>
-        </is>
-      </c>
-      <c r="AH1" s="9" t="inlineStr">
-        <is>
-          <t>fit_cutoff</t>
-        </is>
-      </c>
-      <c r="AI1" s="9" t="inlineStr">
-        <is>
-          <t>fit_candidates</t>
-        </is>
-      </c>
-      <c r="AJ1" s="9" t="inlineStr">
-        <is>
-          <t>freq_model</t>
-        </is>
-      </c>
-      <c r="AK1" s="9" t="inlineStr">
-        <is>
-          <t>ev_freq_source</t>
-        </is>
-      </c>
-      <c r="AL1" s="9" t="inlineStr">
-        <is>
-          <t>sl_attritional_threshold</t>
-        </is>
-      </c>
-      <c r="AM1" s="9" t="inlineStr">
-        <is>
-          <t>sl_cov_floor</t>
-        </is>
-      </c>
-      <c r="AN1" s="9" t="inlineStr">
-        <is>
-          <t>sl_attritional_dist</t>
-        </is>
-      </c>
-      <c r="AO1" s="9" t="inlineStr">
-        <is>
-          <t>net_claims_budget</t>
-        </is>
-      </c>
-      <c r="AP1" s="9" t="inlineStr">
-        <is>
-          <t>reference_lives</t>
-        </is>
-      </c>
-      <c r="AQ1" s="9" t="inlineStr">
-        <is>
-          <t>return_periods</t>
-        </is>
-      </c>
-      <c r="AR1" s="9" t="inlineStr">
-        <is>
-          <t>currency_display</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -9044,38 +11674,238 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:AT1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>cover</t>
+          <t>cedant</t>
         </is>
       </c>
       <c r="B1" s="9" t="inlineStr">
         <is>
-          <t>reinsurer_expense_pct</t>
+          <t>country</t>
         </is>
       </c>
       <c r="C1" s="9" t="inlineStr">
         <is>
-          <t>brokerage_pct</t>
+          <t>line</t>
         </is>
       </c>
       <c r="D1" s="9" t="inlineStr">
         <is>
-          <t>profit_margin_pct</t>
+          <t>quote_ccy</t>
         </is>
       </c>
       <c r="E1" s="9" t="inlineStr">
         <is>
-          <t>premium_tax_pct</t>
+          <t>fx_quote_to_usd</t>
         </is>
       </c>
       <c r="F1" s="9" t="inlineStr">
         <is>
-          <t>risk_load_k</t>
+          <t>treaty_start</t>
+        </is>
+      </c>
+      <c r="G1" s="9" t="inlineStr">
+        <is>
+          <t>quote_year</t>
+        </is>
+      </c>
+      <c r="H1" s="9" t="inlineStr">
+        <is>
+          <t>run_label</t>
+        </is>
+      </c>
+      <c r="I1" s="9" t="inlineStr">
+        <is>
+          <t>scenario_id</t>
+        </is>
+      </c>
+      <c r="J1" s="9" t="inlineStr">
+        <is>
+          <t>source_mode</t>
+        </is>
+      </c>
+      <c r="K1" s="9" t="inlineStr">
+        <is>
+          <t>premium_basis</t>
+        </is>
+      </c>
+      <c r="L1" s="9" t="inlineStr">
+        <is>
+          <t>segment_field</t>
+        </is>
+      </c>
+      <c r="M1" s="9" t="inlineStr">
+        <is>
+          <t>ete_tpa_filter</t>
+        </is>
+      </c>
+      <c r="N1" s="9" t="inlineStr">
+        <is>
+          <t>treaty_basis</t>
+        </is>
+      </c>
+      <c r="O1" s="9" t="inlineStr">
+        <is>
+          <t>claims_trigger</t>
+        </is>
+      </c>
+      <c r="P1" s="9" t="inlineStr">
+        <is>
+          <t>paid_runoff_months</t>
+        </is>
+      </c>
+      <c r="Q1" s="9" t="inlineStr">
+        <is>
+          <t>pp_accumulation</t>
+        </is>
+      </c>
+      <c r="R1" s="9" t="inlineStr">
+        <is>
+          <t>epi_quote_year</t>
+        </is>
+      </c>
+      <c r="S1" s="9" t="inlineStr">
+        <is>
+          <t>expected_lives_quote_year</t>
+        </is>
+      </c>
+      <c r="T1" s="9" t="inlineStr">
+        <is>
+          <t>years_included</t>
+        </is>
+      </c>
+      <c r="U1" s="9" t="inlineStr">
+        <is>
+          <t>output_threshold_pct_min_ap</t>
+        </is>
+      </c>
+      <c r="V1" s="9" t="inlineStr">
+        <is>
+          <t>policy_limit</t>
+        </is>
+      </c>
+      <c r="W1" s="9" t="inlineStr">
+        <is>
+          <t>outlier_method</t>
+        </is>
+      </c>
+      <c r="X1" s="9" t="inlineStr">
+        <is>
+          <t>outlier_value</t>
+        </is>
+      </c>
+      <c r="Y1" s="9" t="inlineStr">
+        <is>
+          <t>iqr_multiplier</t>
+        </is>
+      </c>
+      <c r="Z1" s="9" t="inlineStr">
+        <is>
+          <t>full_cred_n</t>
+        </is>
+      </c>
+      <c r="AA1" s="9" t="inlineStr">
+        <is>
+          <t>complement_source</t>
+        </is>
+      </c>
+      <c r="AB1" s="9" t="inlineStr">
+        <is>
+          <t>benchmark_rate</t>
+        </is>
+      </c>
+      <c r="AC1" s="9" t="inlineStr">
+        <is>
+          <t>incidence_adj</t>
+        </is>
+      </c>
+      <c r="AD1" s="9" t="inlineStr">
+        <is>
+          <t>qs_cedant_retention_pct</t>
+        </is>
+      </c>
+      <c r="AE1" s="9" t="inlineStr">
+        <is>
+          <t>evaluate_mode</t>
+        </is>
+      </c>
+      <c r="AF1" s="9" t="inlineStr">
+        <is>
+          <t>iterations</t>
+        </is>
+      </c>
+      <c r="AG1" s="9" t="inlineStr">
+        <is>
+          <t>seed</t>
+        </is>
+      </c>
+      <c r="AH1" s="9" t="inlineStr">
+        <is>
+          <t>fit_cutoff</t>
+        </is>
+      </c>
+      <c r="AI1" s="9" t="inlineStr">
+        <is>
+          <t>fit_candidates</t>
+        </is>
+      </c>
+      <c r="AJ1" s="9" t="inlineStr">
+        <is>
+          <t>fit_selected</t>
+        </is>
+      </c>
+      <c r="AK1" s="9" t="inlineStr">
+        <is>
+          <t>severity_source</t>
+        </is>
+      </c>
+      <c r="AL1" s="9" t="inlineStr">
+        <is>
+          <t>freq_model</t>
+        </is>
+      </c>
+      <c r="AM1" s="9" t="inlineStr">
+        <is>
+          <t>ev_freq_source</t>
+        </is>
+      </c>
+      <c r="AN1" s="9" t="inlineStr">
+        <is>
+          <t>sl_attritional_threshold</t>
+        </is>
+      </c>
+      <c r="AO1" s="9" t="inlineStr">
+        <is>
+          <t>sl_cov_floor</t>
+        </is>
+      </c>
+      <c r="AP1" s="9" t="inlineStr">
+        <is>
+          <t>sl_attritional_dist</t>
+        </is>
+      </c>
+      <c r="AQ1" s="9" t="inlineStr">
+        <is>
+          <t>net_claims_budget</t>
+        </is>
+      </c>
+      <c r="AR1" s="9" t="inlineStr">
+        <is>
+          <t>reference_lives</t>
+        </is>
+      </c>
+      <c r="AS1" s="9" t="inlineStr">
+        <is>
+          <t>return_periods</t>
+        </is>
+      </c>
+      <c r="AT1" s="9" t="inlineStr">
+        <is>
+          <t>currency_display</t>
         </is>
       </c>
     </row>

--- a/excel/templates/XoL_Results.xlsx
+++ b/excel/templates/XoL_Results.xlsx
@@ -60,6 +60,7 @@
     <definedName name="pa_premium_basis">INDEX(INDIRECT("'out_params'!$A$2:$BZ$60000"),0,MATCH("premium_basis",INDIRECT("'out_params'!$A$1:$BZ$1"),0))</definedName>
     <definedName name="pa_segment_field">INDEX(INDIRECT("'out_params'!$A$2:$BZ$60000"),0,MATCH("segment_field",INDIRECT("'out_params'!$A$1:$BZ$1"),0))</definedName>
     <definedName name="pa_ete_tpa_filter">INDEX(INDIRECT("'out_params'!$A$2:$BZ$60000"),0,MATCH("ete_tpa_filter",INDIRECT("'out_params'!$A$1:$BZ$1"),0))</definedName>
+    <definedName name="pa_ete_payer_filter">INDEX(INDIRECT("'out_params'!$A$2:$BZ$60000"),0,MATCH("ete_payer_filter",INDIRECT("'out_params'!$A$1:$BZ$1"),0))</definedName>
     <definedName name="pa_treaty_basis">INDEX(INDIRECT("'out_params'!$A$2:$BZ$60000"),0,MATCH("treaty_basis",INDIRECT("'out_params'!$A$1:$BZ$1"),0))</definedName>
     <definedName name="pa_claims_trigger">INDEX(INDIRECT("'out_params'!$A$2:$BZ$60000"),0,MATCH("claims_trigger",INDIRECT("'out_params'!$A$1:$BZ$1"),0))</definedName>
     <definedName name="pa_paid_runoff_months">INDEX(INDIRECT("'out_params'!$A$2:$BZ$60000"),0,MATCH("paid_runoff_months",INDIRECT("'out_params'!$A$1:$BZ$1"),0))</definedName>
@@ -11674,7 +11675,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT1"/>
+  <dimension ref="A1:AU1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11745,165 +11746,170 @@
       </c>
       <c r="N1" s="9" t="inlineStr">
         <is>
+          <t>ete_payer_filter</t>
+        </is>
+      </c>
+      <c r="O1" s="9" t="inlineStr">
+        <is>
           <t>treaty_basis</t>
         </is>
       </c>
-      <c r="O1" s="9" t="inlineStr">
+      <c r="P1" s="9" t="inlineStr">
         <is>
           <t>claims_trigger</t>
         </is>
       </c>
-      <c r="P1" s="9" t="inlineStr">
+      <c r="Q1" s="9" t="inlineStr">
         <is>
           <t>paid_runoff_months</t>
         </is>
       </c>
-      <c r="Q1" s="9" t="inlineStr">
+      <c r="R1" s="9" t="inlineStr">
         <is>
           <t>pp_accumulation</t>
         </is>
       </c>
-      <c r="R1" s="9" t="inlineStr">
+      <c r="S1" s="9" t="inlineStr">
         <is>
           <t>epi_quote_year</t>
         </is>
       </c>
-      <c r="S1" s="9" t="inlineStr">
+      <c r="T1" s="9" t="inlineStr">
         <is>
           <t>expected_lives_quote_year</t>
         </is>
       </c>
-      <c r="T1" s="9" t="inlineStr">
+      <c r="U1" s="9" t="inlineStr">
         <is>
           <t>years_included</t>
         </is>
       </c>
-      <c r="U1" s="9" t="inlineStr">
+      <c r="V1" s="9" t="inlineStr">
         <is>
           <t>output_threshold_pct_min_ap</t>
         </is>
       </c>
-      <c r="V1" s="9" t="inlineStr">
+      <c r="W1" s="9" t="inlineStr">
         <is>
           <t>policy_limit</t>
         </is>
       </c>
-      <c r="W1" s="9" t="inlineStr">
+      <c r="X1" s="9" t="inlineStr">
         <is>
           <t>outlier_method</t>
         </is>
       </c>
-      <c r="X1" s="9" t="inlineStr">
+      <c r="Y1" s="9" t="inlineStr">
         <is>
           <t>outlier_value</t>
         </is>
       </c>
-      <c r="Y1" s="9" t="inlineStr">
+      <c r="Z1" s="9" t="inlineStr">
         <is>
           <t>iqr_multiplier</t>
         </is>
       </c>
-      <c r="Z1" s="9" t="inlineStr">
+      <c r="AA1" s="9" t="inlineStr">
         <is>
           <t>full_cred_n</t>
         </is>
       </c>
-      <c r="AA1" s="9" t="inlineStr">
+      <c r="AB1" s="9" t="inlineStr">
         <is>
           <t>complement_source</t>
         </is>
       </c>
-      <c r="AB1" s="9" t="inlineStr">
+      <c r="AC1" s="9" t="inlineStr">
         <is>
           <t>benchmark_rate</t>
         </is>
       </c>
-      <c r="AC1" s="9" t="inlineStr">
+      <c r="AD1" s="9" t="inlineStr">
         <is>
           <t>incidence_adj</t>
         </is>
       </c>
-      <c r="AD1" s="9" t="inlineStr">
+      <c r="AE1" s="9" t="inlineStr">
         <is>
           <t>qs_cedant_retention_pct</t>
         </is>
       </c>
-      <c r="AE1" s="9" t="inlineStr">
+      <c r="AF1" s="9" t="inlineStr">
         <is>
           <t>evaluate_mode</t>
         </is>
       </c>
-      <c r="AF1" s="9" t="inlineStr">
+      <c r="AG1" s="9" t="inlineStr">
         <is>
           <t>iterations</t>
         </is>
       </c>
-      <c r="AG1" s="9" t="inlineStr">
+      <c r="AH1" s="9" t="inlineStr">
         <is>
           <t>seed</t>
         </is>
       </c>
-      <c r="AH1" s="9" t="inlineStr">
+      <c r="AI1" s="9" t="inlineStr">
         <is>
           <t>fit_cutoff</t>
         </is>
       </c>
-      <c r="AI1" s="9" t="inlineStr">
+      <c r="AJ1" s="9" t="inlineStr">
         <is>
           <t>fit_candidates</t>
         </is>
       </c>
-      <c r="AJ1" s="9" t="inlineStr">
+      <c r="AK1" s="9" t="inlineStr">
         <is>
           <t>fit_selected</t>
         </is>
       </c>
-      <c r="AK1" s="9" t="inlineStr">
+      <c r="AL1" s="9" t="inlineStr">
         <is>
           <t>severity_source</t>
         </is>
       </c>
-      <c r="AL1" s="9" t="inlineStr">
+      <c r="AM1" s="9" t="inlineStr">
         <is>
           <t>freq_model</t>
         </is>
       </c>
-      <c r="AM1" s="9" t="inlineStr">
+      <c r="AN1" s="9" t="inlineStr">
         <is>
           <t>ev_freq_source</t>
         </is>
       </c>
-      <c r="AN1" s="9" t="inlineStr">
+      <c r="AO1" s="9" t="inlineStr">
         <is>
           <t>sl_attritional_threshold</t>
         </is>
       </c>
-      <c r="AO1" s="9" t="inlineStr">
+      <c r="AP1" s="9" t="inlineStr">
         <is>
           <t>sl_cov_floor</t>
         </is>
       </c>
-      <c r="AP1" s="9" t="inlineStr">
+      <c r="AQ1" s="9" t="inlineStr">
         <is>
           <t>sl_attritional_dist</t>
         </is>
       </c>
-      <c r="AQ1" s="9" t="inlineStr">
+      <c r="AR1" s="9" t="inlineStr">
         <is>
           <t>net_claims_budget</t>
         </is>
       </c>
-      <c r="AR1" s="9" t="inlineStr">
+      <c r="AS1" s="9" t="inlineStr">
         <is>
           <t>reference_lives</t>
         </is>
       </c>
-      <c r="AS1" s="9" t="inlineStr">
+      <c r="AT1" s="9" t="inlineStr">
         <is>
           <t>return_periods</t>
         </is>
       </c>
-      <c r="AT1" s="9" t="inlineStr">
+      <c r="AU1" s="9" t="inlineStr">
         <is>
           <t>currency_display</t>
         </is>
